--- a/E/CLB07N.xlsx
+++ b/E/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="769">
   <si>
     <t/>
   </si>
@@ -865,43 +865,58 @@
     <t>PUCUK/H TEH L/SGR500</t>
   </si>
   <si>
+    <t>10036640</t>
+  </si>
+  <si>
+    <t>TEH KOTAK JASMINE300</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20048435</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LESS/S 300</t>
+  </si>
+  <si>
+    <t>20143447</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH ORI 300</t>
+  </si>
+  <si>
+    <t>20143446</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR300</t>
+  </si>
+  <si>
+    <t>20044334</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BTL TPK300</t>
+  </si>
+  <si>
+    <t>10005128</t>
+  </si>
+  <si>
+    <t>SOSRO TEH KOTAK B250</t>
+  </si>
+  <si>
+    <t>20024315</t>
+  </si>
+  <si>
+    <t>TEH BOTOL LS.SGR 250</t>
+  </si>
+  <si>
     <t>20026226</t>
   </si>
   <si>
     <t>ULTRA TEH KOTAK 500</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>10036640</t>
-  </si>
-  <si>
-    <t>TEH KOTAK JASMINE300</t>
-  </si>
-  <si>
-    <t>20048435</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LESS/S 300</t>
-  </si>
-  <si>
-    <t>20044334</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK300</t>
-  </si>
-  <si>
-    <t>10005128</t>
-  </si>
-  <si>
-    <t>SOSRO TEH KOTAK B250</t>
-  </si>
-  <si>
-    <t>20024315</t>
-  </si>
-  <si>
-    <t>TEH BOTOL LS.SGR 250</t>
+    <t>19</t>
   </si>
   <si>
     <t>20100142</t>
@@ -910,9 +925,6 @@
     <t>TEH KOTAK BLCKCR 300</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
     <t>20100143</t>
   </si>
   <si>
@@ -2306,21 +2318,6 @@
   </si>
   <si>
     <t>NESTLE PURE LIFE 600</t>
-  </si>
-  <si>
-    <t>20135462</t>
-  </si>
-  <si>
-    <t>DNCW MLKY CKS&amp;CRM180</t>
-  </si>
-  <si>
-    <t>998</t>
-  </si>
-  <si>
-    <t>20135463</t>
-  </si>
-  <si>
-    <t>DNCW MLKY CHO.HZL180</t>
   </si>
 </sst>
 </file>
@@ -2719,8 +2716,7 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="5" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="4" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5455,10 +5451,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>23</v>
@@ -5466,19 +5462,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="C138" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="E138" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>23</v>
@@ -5495,10 +5491,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>23</v>
@@ -5515,10 +5511,10 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>23</v>
@@ -5535,10 +5531,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>23</v>
@@ -5555,13 +5551,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -5575,13 +5571,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -5595,53 +5591,53 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="C146" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="C146" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="E146" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -5655,13 +5651,13 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -5675,13 +5671,13 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -5695,10 +5691,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>23</v>
@@ -5715,13 +5711,13 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -5735,10 +5731,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>23</v>
@@ -5755,10 +5751,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>23</v>
@@ -5766,19 +5762,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>333</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>23</v>
@@ -5786,19 +5782,19 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>331</v>
-      </c>
       <c r="E154" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>23</v>
@@ -5815,10 +5811,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>23</v>
@@ -5835,10 +5831,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>23</v>
@@ -5855,10 +5851,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>23</v>
@@ -5875,13 +5871,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -5895,13 +5891,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5915,10 +5911,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>31</v>
@@ -5935,53 +5931,53 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="C163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="E163" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5995,10 +5991,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>23</v>
@@ -6015,13 +6011,13 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -6035,10 +6031,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>23</v>
@@ -6055,10 +6051,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>23</v>
@@ -6075,10 +6071,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>23</v>
@@ -6095,10 +6091,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>23</v>
@@ -6106,19 +6102,19 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>369</v>
-      </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>23</v>
@@ -6126,19 +6122,19 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B171" s="1" t="s">
+      <c r="C171" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="C171" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="E171" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>23</v>
@@ -6155,10 +6151,10 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>23</v>
@@ -6175,10 +6171,10 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>23</v>
@@ -6195,10 +6191,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>23</v>
@@ -6215,10 +6211,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>23</v>
@@ -6235,30 +6231,30 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>384</v>
-      </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>23</v>
@@ -6266,22 +6262,22 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="E178" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -6295,53 +6291,53 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>389</v>
+        <v>23</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>391</v>
-      </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>389</v>
+        <v>23</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="C181" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F181" s="1" t="s">
         <v>393</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F181" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -6355,13 +6351,13 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>28</v>
+        <v>393</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -6375,13 +6371,13 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6395,53 +6391,53 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B186" s="1" t="s">
+      <c r="C186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="C186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="E186" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -6455,13 +6451,13 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6475,13 +6471,13 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6495,13 +6491,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6515,13 +6511,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6535,13 +6531,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6555,13 +6551,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -6575,10 +6571,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>23</v>
@@ -6586,19 +6582,19 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B194" s="1" t="s">
-        <v>421</v>
-      </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>23</v>
@@ -6606,19 +6602,19 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="C195" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="C195" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="E195" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>23</v>
@@ -6635,10 +6631,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>23</v>
@@ -6655,10 +6651,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>23</v>
@@ -6675,10 +6671,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>23</v>
@@ -6695,10 +6691,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>23</v>
@@ -6715,10 +6711,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>23</v>
@@ -6735,10 +6731,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>23</v>
@@ -6755,10 +6751,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>23</v>
@@ -6766,19 +6762,19 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B203" s="1" t="s">
-        <v>440</v>
-      </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>23</v>
@@ -6786,19 +6782,19 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="B204" s="1" t="s">
+      <c r="C204" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D204" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="C204" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="E204" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>23</v>
@@ -6815,10 +6811,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>23</v>
@@ -6835,10 +6831,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>23</v>
@@ -6855,10 +6851,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>23</v>
@@ -6875,10 +6871,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>23</v>
@@ -6895,10 +6891,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>23</v>
@@ -6915,10 +6911,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>23</v>
@@ -6935,10 +6931,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>23</v>
@@ -6946,19 +6942,19 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="B212" s="1" t="s">
-        <v>459</v>
-      </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>23</v>
@@ -6966,19 +6962,19 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="B213" s="1" t="s">
+      <c r="C213" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D213" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="C213" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>457</v>
-      </c>
       <c r="E213" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>23</v>
@@ -6995,10 +6991,10 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>23</v>
@@ -7015,10 +7011,10 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>23</v>
@@ -7035,10 +7031,10 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>23</v>
@@ -7055,10 +7051,10 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>23</v>
@@ -7075,13 +7071,13 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -7095,10 +7091,10 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>23</v>
@@ -7115,30 +7111,30 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="B221" s="1" t="s">
-        <v>478</v>
-      </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>23</v>
@@ -7146,19 +7142,19 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="B222" s="1" t="s">
+      <c r="C222" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D222" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="C222" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D222" s="1" t="s">
-        <v>476</v>
-      </c>
       <c r="E222" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>23</v>
@@ -7175,10 +7171,10 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>23</v>
@@ -7195,13 +7191,13 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -7215,13 +7211,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -7235,13 +7231,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>164</v>
+        <v>31</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -7255,13 +7251,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>164</v>
+        <v>31</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -7275,50 +7271,50 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>31</v>
+        <v>164</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="B229" s="1" t="s">
-        <v>495</v>
-      </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>31</v>
+        <v>164</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="B230" s="1" t="s">
+      <c r="C230" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D230" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="C230" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D230" s="1" t="s">
-        <v>493</v>
-      </c>
       <c r="E230" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>31</v>
@@ -7335,10 +7331,10 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>31</v>
@@ -7355,10 +7351,10 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F232" s="1" t="s">
         <v>31</v>
@@ -7375,13 +7371,13 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -7395,13 +7391,13 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -7415,50 +7411,50 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B236" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="B236" s="1" t="s">
-        <v>510</v>
-      </c>
       <c r="C236" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B237" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="B237" s="1" t="s">
+      <c r="C237" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D237" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="C237" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D237" s="1" t="s">
-        <v>508</v>
-      </c>
       <c r="E237" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>31</v>
@@ -7475,13 +7471,13 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>164</v>
+        <v>31</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -7495,53 +7491,53 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>517</v>
+        <v>31</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B240" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="B240" s="1" t="s">
-        <v>519</v>
-      </c>
       <c r="C240" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>28</v>
+        <v>164</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B241" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="B241" s="1" t="s">
+      <c r="C241" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D241" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F241" s="1" t="s">
         <v>521</v>
-      </c>
-      <c r="C241" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D241" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="E241" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F241" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -7555,10 +7551,10 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F242" s="1" t="s">
         <v>28</v>
@@ -7575,10 +7571,10 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>23</v>
@@ -7595,30 +7591,30 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B245" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="B245" s="1" t="s">
-        <v>530</v>
-      </c>
       <c r="C245" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>23</v>
@@ -7626,19 +7622,19 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B246" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="B246" s="1" t="s">
+      <c r="C246" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D246" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="C246" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D246" s="1" t="s">
-        <v>528</v>
-      </c>
       <c r="E246" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>23</v>
@@ -7655,10 +7651,10 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>23</v>
@@ -7675,13 +7671,13 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -7695,13 +7691,13 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7715,13 +7711,13 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -7735,10 +7731,10 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>31</v>
@@ -7755,50 +7751,50 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B253" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="B253" s="1" t="s">
-        <v>547</v>
-      </c>
       <c r="C253" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B254" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="B254" s="1" t="s">
+      <c r="C254" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D254" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="C254" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D254" s="1" t="s">
-        <v>545</v>
-      </c>
       <c r="E254" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>23</v>
@@ -7815,10 +7811,10 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>23</v>
@@ -7835,13 +7831,13 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -7855,10 +7851,10 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>23</v>
@@ -7875,13 +7871,13 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7895,10 +7891,10 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F259" s="1" t="s">
         <v>23</v>
@@ -7915,33 +7911,33 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="B261" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="B261" s="1" t="s">
-        <v>561</v>
-      </c>
       <c r="C261" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7955,33 +7951,33 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D263" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="B263" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="C263" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D263" s="1" t="s">
-        <v>562</v>
-      </c>
       <c r="E263" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -7995,10 +7991,10 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>23</v>
@@ -8015,10 +8011,10 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>23</v>
@@ -8035,10 +8031,10 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>23</v>
@@ -8055,10 +8051,10 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>23</v>
@@ -8075,10 +8071,10 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>23</v>
@@ -8095,10 +8091,10 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>23</v>
@@ -8106,19 +8102,19 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B270" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="B270" s="1" t="s">
-        <v>582</v>
-      </c>
       <c r="C270" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>23</v>
@@ -8126,19 +8122,19 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B271" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="B271" s="1" t="s">
+      <c r="C271" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D271" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="C271" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D271" s="1" t="s">
-        <v>580</v>
-      </c>
       <c r="E271" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>23</v>
@@ -8155,10 +8151,10 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>23</v>
@@ -8175,10 +8171,10 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>23</v>
@@ -8195,10 +8191,10 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>23</v>
@@ -8215,10 +8211,10 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>23</v>
@@ -8235,10 +8231,10 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>23</v>
@@ -8255,10 +8251,10 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>23</v>
@@ -8275,10 +8271,10 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>23</v>
@@ -8295,10 +8291,10 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>163</v>
+        <v>58</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>23</v>
@@ -8315,10 +8311,10 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>603</v>
+        <v>584</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>4</v>
+        <v>142</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>23</v>
@@ -8326,19 +8322,19 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="B281" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="B281" s="1" t="s">
-        <v>605</v>
-      </c>
       <c r="C281" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>603</v>
+        <v>584</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>8</v>
+        <v>163</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>23</v>
@@ -8346,19 +8342,19 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B282" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="B282" s="1" t="s">
+      <c r="C282" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D282" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="C282" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="E282" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>23</v>
@@ -8375,10 +8371,10 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>23</v>
@@ -8395,10 +8391,10 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>23</v>
@@ -8415,10 +8411,10 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>23</v>
@@ -8435,30 +8431,30 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>616</v>
+        <v>23</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="B287" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="B287" s="1" t="s">
-        <v>618</v>
-      </c>
       <c r="C287" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>23</v>
@@ -8466,22 +8462,22 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B288" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="B288" s="1" t="s">
+      <c r="C288" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D288" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E288" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F288" s="1" t="s">
         <v>620</v>
-      </c>
-      <c r="C288" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D288" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="E288" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F288" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -8495,10 +8491,10 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>23</v>
@@ -8515,53 +8511,53 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>625</v>
+        <v>607</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>616</v>
+        <v>23</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="B291" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="B291" s="1" t="s">
-        <v>627</v>
-      </c>
       <c r="C291" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>625</v>
+        <v>607</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>616</v>
+        <v>23</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B292" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="B292" s="1" t="s">
+      <c r="C292" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D292" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="C292" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D292" s="1" t="s">
-        <v>625</v>
-      </c>
       <c r="E292" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8575,13 +8571,13 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8595,13 +8591,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8615,13 +8611,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8635,13 +8631,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8655,13 +8651,13 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8675,13 +8671,13 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8695,50 +8691,50 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>644</v>
+        <v>629</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>23</v>
+        <v>620</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="B300" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="B300" s="1" t="s">
-        <v>646</v>
-      </c>
       <c r="C300" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>644</v>
+        <v>629</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>23</v>
+        <v>620</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B301" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="B301" s="1" t="s">
+      <c r="C301" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D301" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="C301" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D301" s="1" t="s">
-        <v>644</v>
-      </c>
       <c r="E301" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>23</v>
@@ -8755,10 +8751,10 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>23</v>
@@ -8775,10 +8771,10 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>23</v>
@@ -8795,10 +8791,10 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>23</v>
@@ -8815,10 +8811,10 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>23</v>
@@ -8835,10 +8831,10 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>23</v>
@@ -8855,10 +8851,10 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>23</v>
@@ -8875,10 +8871,10 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>23</v>
@@ -8895,10 +8891,10 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>23</v>
@@ -8906,19 +8902,19 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B310" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="B310" s="1" t="s">
-        <v>667</v>
-      </c>
       <c r="C310" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>23</v>
@@ -8926,19 +8922,19 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B311" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="B311" s="1" t="s">
+      <c r="C311" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D311" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="C311" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D311" s="1" t="s">
-        <v>665</v>
-      </c>
       <c r="E311" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>23</v>
@@ -8955,10 +8951,10 @@
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>23</v>
@@ -8975,10 +8971,10 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>23</v>
@@ -8995,10 +8991,10 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>23</v>
@@ -9015,10 +9011,10 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>23</v>
@@ -9035,10 +9031,10 @@
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>23</v>
@@ -9055,10 +9051,10 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>23</v>
@@ -9075,10 +9071,10 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>684</v>
+        <v>669</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>23</v>
@@ -9086,19 +9082,19 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="B319" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="B319" s="1" t="s">
-        <v>686</v>
-      </c>
       <c r="C319" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>684</v>
+        <v>669</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>23</v>
@@ -9106,19 +9102,19 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="B320" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="B320" s="1" t="s">
+      <c r="C320" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D320" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="C320" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D320" s="1" t="s">
-        <v>684</v>
-      </c>
       <c r="E320" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>23</v>
@@ -9135,10 +9131,10 @@
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>23</v>
@@ -9155,10 +9151,10 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>23</v>
@@ -9175,10 +9171,10 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>23</v>
@@ -9195,10 +9191,10 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>23</v>
@@ -9215,10 +9211,10 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>23</v>
@@ -9235,10 +9231,10 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>701</v>
+        <v>688</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>23</v>
@@ -9246,19 +9242,19 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="B327" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="B327" s="1" t="s">
-        <v>703</v>
-      </c>
       <c r="C327" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>701</v>
+        <v>688</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>23</v>
@@ -9266,22 +9262,22 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B328" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="B328" s="1" t="s">
+      <c r="C328" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D328" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="C328" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>701</v>
-      </c>
       <c r="E328" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -9295,13 +9291,13 @@
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -9315,13 +9311,13 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -9335,13 +9331,13 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -9355,10 +9351,10 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>23</v>
@@ -9375,10 +9371,10 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>23</v>
@@ -9395,10 +9391,10 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>23</v>
@@ -9415,10 +9411,10 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>23</v>
@@ -9435,53 +9431,53 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>722</v>
+        <v>705</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B337" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="B337" s="1" t="s">
-        <v>724</v>
-      </c>
       <c r="C337" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>722</v>
+        <v>705</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="B338" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="B338" s="1" t="s">
+      <c r="C338" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D338" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="C338" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D338" s="1" t="s">
-        <v>722</v>
-      </c>
       <c r="E338" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -9495,10 +9491,10 @@
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F339" s="1" t="s">
         <v>31</v>
@@ -9515,10 +9511,10 @@
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F340" s="1" t="s">
         <v>23</v>
@@ -9535,13 +9531,13 @@
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -9555,13 +9551,13 @@
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -9575,93 +9571,93 @@
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>737</v>
+        <v>23</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="B344" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="B344" s="1" t="s">
-        <v>739</v>
-      </c>
       <c r="C344" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B345" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="B345" s="1" t="s">
+      <c r="C345" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D345" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="E345" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F345" s="1" t="s">
         <v>741</v>
-      </c>
-      <c r="C345" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D345" s="1" t="s">
-        <v>742</v>
-      </c>
-      <c r="E345" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F345" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="B346" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="B346" s="1" t="s">
-        <v>744</v>
-      </c>
       <c r="C346" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>742</v>
+        <v>726</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="B347" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="B347" s="1" t="s">
+      <c r="C347" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D347" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="C347" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D347" s="1" t="s">
-        <v>742</v>
-      </c>
       <c r="E347" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>164</v>
+        <v>23</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -9675,10 +9671,10 @@
         <v>3</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F348" s="1" t="s">
         <v>23</v>
@@ -9686,139 +9682,139 @@
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="B349" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="B349" s="1" t="s">
-        <v>751</v>
-      </c>
       <c r="C349" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>28</v>
+        <v>164</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B350" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="C350" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D350" s="1" t="s">
         <v>753</v>
-      </c>
-      <c r="B350" s="1" t="s">
-        <v>754</v>
-      </c>
-      <c r="C350" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D350" s="1" t="s">
-        <v>755</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>756</v>
+        <v>23</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>759</v>
+        <v>28</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D352" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="E352" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F352" s="1" t="s">
         <v>760</v>
-      </c>
-      <c r="B352" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="C352" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D352" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="E352" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F352" s="1" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="C353" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D353" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="E353" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F353" s="1" t="s">
         <v>763</v>
-      </c>
-      <c r="B353" s="1" t="s">
-        <v>764</v>
-      </c>
-      <c r="C353" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D353" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="E353" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F353" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="B354" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="B354" s="1" t="s">
+      <c r="C354" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="E354" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F354" s="1" t="s">
         <v>766</v>
-      </c>
-      <c r="C354" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D354" s="1" t="s">
-        <v>767</v>
-      </c>
-      <c r="E354" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F354" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="B355" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="B355" s="1" t="s">
-        <v>769</v>
-      </c>
       <c r="C355" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F355" s="1" t="s">
         <v>23</v>

--- a/E/CLB07N.xlsx
+++ b/E/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="772">
   <si>
     <t/>
   </si>
@@ -379,6 +379,75 @@
     <t>ABC MILK COFFEE 180</t>
   </si>
   <si>
+    <t>20078206</t>
+  </si>
+  <si>
+    <t>LUWAK WHT ORGL 220ML</t>
+  </si>
+  <si>
+    <t>20120904</t>
+  </si>
+  <si>
+    <t>KK BLACK AREN 220ML</t>
+  </si>
+  <si>
+    <t>20120906</t>
+  </si>
+  <si>
+    <t>KK MANTANCINO 220ML</t>
+  </si>
+  <si>
+    <t>20133409</t>
+  </si>
+  <si>
+    <t>KK CAFFE LATTE 200ML</t>
+  </si>
+  <si>
+    <t>20138168</t>
+  </si>
+  <si>
+    <t>KK CHEESE LATTEE 200</t>
+  </si>
+  <si>
+    <t>20138167</t>
+  </si>
+  <si>
+    <t>KK JPNS MATCHA 200</t>
+  </si>
+  <si>
+    <t>20129108</t>
+  </si>
+  <si>
+    <t>OATSDE COFFEE 200ML</t>
+  </si>
+  <si>
+    <t>20142499</t>
+  </si>
+  <si>
+    <t>OATSDE ESPR RST 240</t>
+  </si>
+  <si>
+    <t>20134557</t>
+  </si>
+  <si>
+    <t>OATSIDE CRML MCHT200</t>
+  </si>
+  <si>
+    <t>20129123</t>
+  </si>
+  <si>
+    <t>OATSDE CHOCO 200</t>
+  </si>
+  <si>
+    <t>20129102</t>
+  </si>
+  <si>
+    <t>OATSDE BR.BLEND 200</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>20045415</t>
   </si>
   <si>
@@ -391,34 +460,34 @@
     <t>KOPIKO LUCKY DAY 180</t>
   </si>
   <si>
-    <t>20120904</t>
-  </si>
-  <si>
-    <t>KK BLACK AREN 220ML</t>
-  </si>
-  <si>
-    <t>20120906</t>
-  </si>
-  <si>
-    <t>KK MANTANCINO 220ML</t>
-  </si>
-  <si>
-    <t>20133409</t>
-  </si>
-  <si>
-    <t>KK CAFFE LATTE 200ML</t>
-  </si>
-  <si>
-    <t>20138168</t>
-  </si>
-  <si>
-    <t>KK CHEESE LATTEE 200</t>
-  </si>
-  <si>
-    <t>20138167</t>
-  </si>
-  <si>
-    <t>KK JPNS MATCHA 200</t>
+    <t>20076770</t>
+  </si>
+  <si>
+    <t>G/DAY CAPPUCCINO 230</t>
+  </si>
+  <si>
+    <t>20045674</t>
+  </si>
+  <si>
+    <t>G/DAY F.MOCACINO 230</t>
+  </si>
+  <si>
+    <t>20045673</t>
+  </si>
+  <si>
+    <t>G/DAY TIRAMISU/B 230</t>
+  </si>
+  <si>
+    <t>20056193</t>
+  </si>
+  <si>
+    <t>GOOD DAY AVCDO/D 230</t>
+  </si>
+  <si>
+    <t>20132329</t>
+  </si>
+  <si>
+    <t>GOOD DAY GRVY CKS230</t>
   </si>
   <si>
     <t>20132760</t>
@@ -433,1891 +502,1831 @@
     <t>CAFINO RTD CPCINO200</t>
   </si>
   <si>
+    <t>20139577</t>
+  </si>
+  <si>
+    <t>PC AREN LATTE 210ML</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20139578</t>
+  </si>
+  <si>
+    <t>PC GOLDN CARAMEL 210</t>
+  </si>
+  <si>
+    <t>20139576</t>
+  </si>
+  <si>
+    <t>PC CRMY CPUCCINO 210</t>
+  </si>
+  <si>
+    <t>20142601</t>
+  </si>
+  <si>
+    <t>NSCAFE MTCHA ESP 220</t>
+  </si>
+  <si>
+    <t>20140431</t>
+  </si>
+  <si>
+    <t>NSCAFE KITKAT LAT220</t>
+  </si>
+  <si>
+    <t>20133058</t>
+  </si>
+  <si>
+    <t>NSCAFE OAT LATTE 220</t>
+  </si>
+  <si>
+    <t>20027768</t>
+  </si>
+  <si>
+    <t>NESCAFE COFF CRM 180</t>
+  </si>
+  <si>
+    <t>20114494</t>
+  </si>
+  <si>
+    <t>NSCAFE CRML MCTO 220</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20114495</t>
+  </si>
+  <si>
+    <t>NESCAFE CPUCCINO 220</t>
+  </si>
+  <si>
+    <t>20114493</t>
+  </si>
+  <si>
+    <t>NESCAFE LATTE 220ML</t>
+  </si>
+  <si>
+    <t>20138057</t>
+  </si>
+  <si>
+    <t>NSCAFE GULA AREN 220</t>
+  </si>
+  <si>
+    <t>20121456</t>
+  </si>
+  <si>
+    <t>NSCAFE ICE BLACK 220</t>
+  </si>
+  <si>
+    <t>20000787</t>
+  </si>
+  <si>
+    <t>NESCAFE ICE.CF OR220</t>
+  </si>
+  <si>
+    <t>20014954</t>
+  </si>
+  <si>
+    <t>NESCAFE ICE.CF MC220</t>
+  </si>
+  <si>
+    <t>20000786</t>
+  </si>
+  <si>
+    <t>NESCAFE ICE.CF LT220</t>
+  </si>
+  <si>
+    <t>20125115</t>
+  </si>
+  <si>
+    <t>STARBUCKS LATTE 220</t>
+  </si>
+  <si>
+    <t>20125126</t>
+  </si>
+  <si>
+    <t>STARBUCKS CARAMEL220</t>
+  </si>
+  <si>
+    <t>20014608</t>
+  </si>
+  <si>
+    <t>HRMVTON PSK BUMI 150</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>10006263</t>
+  </si>
+  <si>
+    <t>HEMAVITON ENERGY 150</t>
+  </si>
+  <si>
+    <t>10002602</t>
+  </si>
+  <si>
+    <t>M-150 HEALT DRINK150</t>
+  </si>
+  <si>
+    <t>10002595</t>
+  </si>
+  <si>
+    <t>KRATINGDAENG 150 ML</t>
+  </si>
+  <si>
+    <t>10003427</t>
+  </si>
+  <si>
+    <t>KRATINGDAENG SPR.150</t>
+  </si>
+  <si>
+    <t>20022431</t>
+  </si>
+  <si>
+    <t>RED BULL E/DRNK 250</t>
+  </si>
+  <si>
+    <t>20056989</t>
+  </si>
+  <si>
+    <t>RED BULL GOLD 250ML</t>
+  </si>
+  <si>
+    <t>20138252</t>
+  </si>
+  <si>
+    <t>EXTRA JOSS ULTIMT250</t>
+  </si>
+  <si>
+    <t>20038425</t>
+  </si>
+  <si>
+    <t>NTRIVE/B BLCKRNT 100</t>
+  </si>
+  <si>
+    <t>20071510</t>
+  </si>
+  <si>
+    <t>NTRVE BNCOL LYCH 100</t>
+  </si>
+  <si>
+    <t>20003786</t>
+  </si>
+  <si>
+    <t>NU GREEN TEA HNY 450</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20113059</t>
+  </si>
+  <si>
+    <t>NU YOGURT TEA 450ML</t>
+  </si>
+  <si>
+    <t>20139732</t>
+  </si>
+  <si>
+    <t>NU YOGRT TEA BRY 450</t>
+  </si>
+  <si>
+    <t>20036157</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BOTOL 450</t>
+  </si>
+  <si>
+    <t>20002203</t>
+  </si>
+  <si>
+    <t>SOSRO F.TEA APEL 500</t>
+  </si>
+  <si>
+    <t>20003698</t>
+  </si>
+  <si>
+    <t>SOSRO FR.TEA XTRM500</t>
+  </si>
+  <si>
+    <t>20002205</t>
+  </si>
+  <si>
+    <t>SOSRO F.TEA BLKCR500</t>
+  </si>
+  <si>
+    <t>20134046</t>
+  </si>
+  <si>
+    <t>FRUIT TEA FREEZE 500</t>
+  </si>
+  <si>
+    <t>20126464</t>
+  </si>
+  <si>
+    <t>IDM TEH APL&amp;LYCHE350</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20101897</t>
+  </si>
+  <si>
+    <t>IDM TEH APEL 350ML</t>
+  </si>
+  <si>
+    <t>20132840</t>
+  </si>
+  <si>
+    <t>IDM TEH BLCKCRRNT350</t>
+  </si>
+  <si>
+    <t>20066454</t>
+  </si>
+  <si>
+    <t>FRUIT TEA BLCKCR 350</t>
+  </si>
+  <si>
+    <t>20073495</t>
+  </si>
+  <si>
+    <t>FRUIT TEA FREEZE 350</t>
+  </si>
+  <si>
+    <t>20066455</t>
+  </si>
+  <si>
+    <t>FRUIT TEA APPLE 350</t>
+  </si>
+  <si>
+    <t>20079972</t>
+  </si>
+  <si>
+    <t>FRUIT TEA MRKISA 350</t>
+  </si>
+  <si>
+    <t>20138841</t>
+  </si>
+  <si>
+    <t>POKKA NAT. H.ORG 350</t>
+  </si>
+  <si>
+    <t>20135619</t>
+  </si>
+  <si>
+    <t>TEBS ZERO LYCHEE 300</t>
+  </si>
+  <si>
+    <t>20060207</t>
+  </si>
+  <si>
+    <t>I/OCHA TEH MLATI 350</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20048934</t>
+  </si>
+  <si>
+    <t>I/OCHA GRN TEA 350ML</t>
+  </si>
+  <si>
+    <t>20142077</t>
+  </si>
+  <si>
+    <t>TEH LEMON MADU 350ML</t>
+  </si>
+  <si>
+    <t>20018904</t>
+  </si>
+  <si>
+    <t>NU GREEN TEA HNY 330</t>
+  </si>
+  <si>
+    <t>20053867</t>
+  </si>
+  <si>
+    <t>TEH GELAS BTL 350ML</t>
+  </si>
+  <si>
+    <t>20073396</t>
+  </si>
+  <si>
+    <t>S-TEE BTL 390ML</t>
+  </si>
+  <si>
+    <t>20072249</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BOTOL 350</t>
+  </si>
+  <si>
+    <t>20122278</t>
+  </si>
+  <si>
+    <t>TEH BOTOL LS.SGR 350</t>
+  </si>
+  <si>
+    <t>20082395</t>
+  </si>
+  <si>
+    <t>TEH BOTOL TAWAR 350</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI350</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20048155</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR350</t>
+  </si>
+  <si>
+    <t>20037565</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI500</t>
+  </si>
+  <si>
+    <t>20048348</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR500</t>
+  </si>
+  <si>
+    <t>10036640</t>
+  </si>
+  <si>
+    <t>TEH KOTAK JASMINE300</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20048435</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LESS/S 300</t>
+  </si>
+  <si>
+    <t>20143447</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH ORI 300</t>
+  </si>
+  <si>
+    <t>20143446</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR300</t>
+  </si>
+  <si>
+    <t>20044334</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BTL TPK300</t>
+  </si>
+  <si>
+    <t>10005128</t>
+  </si>
+  <si>
+    <t>SOSRO TEH KOTAK B250</t>
+  </si>
+  <si>
+    <t>20024315</t>
+  </si>
+  <si>
+    <t>TEH BOTOL LS.SGR 250</t>
+  </si>
+  <si>
+    <t>20026226</t>
+  </si>
+  <si>
+    <t>ULTRA TEH KOTAK 500</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20100142</t>
+  </si>
+  <si>
+    <t>TEH KOTAK BLCKCR 300</t>
+  </si>
+  <si>
+    <t>20100143</t>
+  </si>
+  <si>
+    <t>TEH KOTAK APPLE 300</t>
+  </si>
+  <si>
+    <t>20137159</t>
+  </si>
+  <si>
+    <t>TEH KOTAK MANGGA 300</t>
+  </si>
+  <si>
+    <t>20087016</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LEMON 300</t>
+  </si>
+  <si>
+    <t>20135647</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LYCHEE 300</t>
+  </si>
+  <si>
+    <t>20117687</t>
+  </si>
+  <si>
+    <t>DLMNT BOBA MTCHA 240</t>
+  </si>
+  <si>
+    <t>20117682</t>
+  </si>
+  <si>
+    <t>DLMNT BOBA RD.VEL240</t>
+  </si>
+  <si>
+    <t>20080088</t>
+  </si>
+  <si>
+    <t>POKKA GREEN TEA 450</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20036765</t>
+  </si>
+  <si>
+    <t>FRESTEA GRN MADU 500</t>
+  </si>
+  <si>
+    <t>20012574</t>
+  </si>
+  <si>
+    <t>FRESTEA TEH APEL 500</t>
+  </si>
+  <si>
+    <t>20035829</t>
+  </si>
+  <si>
+    <t>TEBS TEA WT/SODA 500</t>
+  </si>
+  <si>
+    <t>20093586</t>
+  </si>
+  <si>
+    <t>ICHTN THAI M.COFF300</t>
+  </si>
+  <si>
+    <t>20136363</t>
+  </si>
+  <si>
+    <t>ICHTN DARK CHOCO 300</t>
+  </si>
+  <si>
+    <t>20135599</t>
+  </si>
+  <si>
+    <t>ICHTAN KRN BANANA300</t>
+  </si>
+  <si>
+    <t>20142025</t>
+  </si>
+  <si>
+    <t>ICHITAN MLN MILK 300</t>
+  </si>
+  <si>
+    <t>20040383</t>
+  </si>
+  <si>
+    <t>NU MILK TEA 330ML</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20069527</t>
+  </si>
+  <si>
+    <t>NU TEH TARIK 330ML</t>
+  </si>
+  <si>
+    <t>20128233</t>
+  </si>
+  <si>
+    <t>NU CHO TEA HZLTEA330</t>
+  </si>
+  <si>
+    <t>20138202</t>
+  </si>
+  <si>
+    <t>NU MATCHA LATTEA 330</t>
+  </si>
+  <si>
+    <t>20141981</t>
+  </si>
+  <si>
+    <t>DUM2 CHO MILK TEA330</t>
+  </si>
+  <si>
+    <t>20141980</t>
+  </si>
+  <si>
+    <t>DUM2 RYL MILK TEA330</t>
+  </si>
+  <si>
+    <t>20085054</t>
+  </si>
+  <si>
+    <t>ICHTN THAI M.TEA 300</t>
+  </si>
+  <si>
+    <t>20101102</t>
+  </si>
+  <si>
+    <t>ICHTN MLK GR.TEA 300</t>
+  </si>
+  <si>
+    <t>20113450</t>
+  </si>
+  <si>
+    <t>ICHITAN MLK BRWN 300</t>
+  </si>
+  <si>
+    <t>20113377</t>
+  </si>
+  <si>
+    <t>FLRDINA COCO BIT 350</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20043877</t>
+  </si>
+  <si>
+    <t>FLORIDINA ORANGE 350</t>
+  </si>
+  <si>
+    <t>20021178</t>
+  </si>
+  <si>
+    <t>MINUTE MAID ORG 300</t>
+  </si>
+  <si>
+    <t>20062818</t>
+  </si>
+  <si>
+    <t>FRUITAMIN LYCHE 350</t>
+  </si>
+  <si>
+    <t>20091654</t>
+  </si>
+  <si>
+    <t>COCO BIT SP.GUAV 350</t>
+  </si>
+  <si>
+    <t>20140331</t>
+  </si>
+  <si>
+    <t>COCO BIT STRAW.S 350</t>
+  </si>
+  <si>
+    <t>20140327</t>
+  </si>
+  <si>
+    <t>COCO BIT KY.GRP 350</t>
+  </si>
+  <si>
+    <t>20140332</t>
+  </si>
+  <si>
+    <t>COCO BIT HOK.MLN 350</t>
+  </si>
+  <si>
+    <t>20042848</t>
+  </si>
+  <si>
+    <t>MOGU MOGU LYCHHE 320</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20047245</t>
+  </si>
+  <si>
+    <t>MOGU MOGU CCONUT 320</t>
+  </si>
+  <si>
+    <t>20076486</t>
+  </si>
+  <si>
+    <t>MOGU MOGU MELON 320</t>
+  </si>
+  <si>
+    <t>20042859</t>
+  </si>
+  <si>
+    <t>MOGU MOGU MANGGA 320</t>
+  </si>
+  <si>
+    <t>20042860</t>
+  </si>
+  <si>
+    <t>MOGU MOGU STRWBRY320</t>
+  </si>
+  <si>
+    <t>20047244</t>
+  </si>
+  <si>
+    <t>MOGU MOGU GRAPE 320</t>
+  </si>
+  <si>
+    <t>20137095</t>
+  </si>
+  <si>
+    <t>MOGU2 BUBBLE GUM 320</t>
+  </si>
+  <si>
+    <t>20136277</t>
+  </si>
+  <si>
+    <t>SNPRD FRT MG.PINE220</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>20134353</t>
+  </si>
+  <si>
+    <t>IDM S/B NNS&amp;MRKSA220</t>
+  </si>
+  <si>
+    <t>20134354</t>
+  </si>
+  <si>
+    <t>IDM SARI BH NANAS220</t>
+  </si>
+  <si>
+    <t>20089805</t>
+  </si>
+  <si>
+    <t>OLATTE PEACH KLG 240</t>
+  </si>
+  <si>
+    <t>RT,(E-2.5B)</t>
+  </si>
+  <si>
+    <t>20089806</t>
+  </si>
+  <si>
+    <t>OLATTE PEAR KLG 240</t>
+  </si>
+  <si>
+    <t>20135975</t>
+  </si>
+  <si>
+    <t>OLATTE STRWB KLG 240</t>
+  </si>
+  <si>
+    <t>20052734</t>
+  </si>
+  <si>
+    <t>LOTTE MILKIS MLN 250</t>
+  </si>
+  <si>
+    <t>10028190</t>
+  </si>
+  <si>
+    <t>LOTTE MILKIS KLG 250</t>
+  </si>
+  <si>
+    <t>10008887</t>
+  </si>
+  <si>
+    <t>ULTRA KCNG HIJAU 250</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>10000278</t>
+  </si>
+  <si>
+    <t>ABC KACANG HIJAU 250</t>
+  </si>
+  <si>
+    <t>20120929</t>
+  </si>
+  <si>
+    <t>PANDA GR.JLY+BSL 310</t>
+  </si>
+  <si>
+    <t>20046319</t>
+  </si>
+  <si>
+    <t>PANDA GRASS JELY310</t>
+  </si>
+  <si>
+    <t>20141495</t>
+  </si>
+  <si>
+    <t>PANDA GRN GRS JEL310</t>
+  </si>
+  <si>
+    <t>20112383</t>
+  </si>
+  <si>
+    <t>MR.NATA JELI LECI126</t>
+  </si>
+  <si>
+    <t>20112382</t>
+  </si>
+  <si>
+    <t>MR.NATA JEL BLU/B126</t>
+  </si>
+  <si>
+    <t>20136250</t>
+  </si>
+  <si>
+    <t>JELE JELLY LYCHEE150</t>
+  </si>
+  <si>
+    <t>20055762</t>
+  </si>
+  <si>
+    <t>JELE COLLAGEN 150G</t>
+  </si>
+  <si>
+    <t>10007970</t>
+  </si>
+  <si>
+    <t>BUAVITA JAMBU SL 245</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>10007974</t>
+  </si>
+  <si>
+    <t>BUAVITA LYCHEE SL245</t>
+  </si>
+  <si>
+    <t>10007971</t>
+  </si>
+  <si>
+    <t>BUAVITA ORANGE SL245</t>
+  </si>
+  <si>
+    <t>10007973</t>
+  </si>
+  <si>
+    <t>BUAVITA MANGGA 245ML</t>
+  </si>
+  <si>
+    <t>10007972</t>
+  </si>
+  <si>
+    <t>BUAVITA JC APPLE 245</t>
+  </si>
+  <si>
+    <t>20140324</t>
+  </si>
+  <si>
+    <t>BUAVITA K.STRAW 245</t>
+  </si>
+  <si>
+    <t>20140328</t>
+  </si>
+  <si>
+    <t>BUAVITA K MS.GRP 245</t>
+  </si>
+  <si>
+    <t>10007385</t>
+  </si>
+  <si>
+    <t>ULTRA SR ASAM SLM250</t>
+  </si>
+  <si>
+    <t>20136649</t>
+  </si>
+  <si>
+    <t>DIAMOND JC CRANBR200</t>
+  </si>
+  <si>
+    <t>20065041</t>
+  </si>
+  <si>
+    <t>PORORO BLUEBERY235ML</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>20037137</t>
+  </si>
+  <si>
+    <t>PORORO STROBRI 235ML</t>
+  </si>
+  <si>
+    <t>20037136</t>
+  </si>
+  <si>
+    <t>PORORO SUSU 235ML</t>
+  </si>
+  <si>
+    <t>20085010</t>
+  </si>
+  <si>
+    <t>PORORO MANGO 235</t>
+  </si>
+  <si>
+    <t>20137094</t>
+  </si>
+  <si>
+    <t>PORORO PEACH 235</t>
+  </si>
+  <si>
+    <t>20141361</t>
+  </si>
+  <si>
+    <t>PORORO ZERO STRW 235</t>
+  </si>
+  <si>
+    <t>20141360</t>
+  </si>
+  <si>
+    <t>PORORO ZERO MILK 235</t>
+  </si>
+  <si>
+    <t>20143468</t>
+  </si>
+  <si>
+    <t>PRRO ZROSGR BLBRY235</t>
+  </si>
+  <si>
+    <t>20069773</t>
+  </si>
+  <si>
+    <t>ISOPLUS BTL 350ML</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>20128918</t>
+  </si>
+  <si>
+    <t>ISOPLUS COCO 350ML</t>
+  </si>
+  <si>
+    <t>20138959</t>
+  </si>
+  <si>
+    <t>IF COCONUT WTR 350ML</t>
+  </si>
+  <si>
+    <t>20142818</t>
+  </si>
+  <si>
+    <t>EWATER GRAPEFRT 555</t>
+  </si>
+  <si>
+    <t>20142819</t>
+  </si>
+  <si>
+    <t>EWATER LEMON 555ML</t>
+  </si>
+  <si>
+    <t>20142862</t>
+  </si>
+  <si>
+    <t>EWATER GRPFRT 380</t>
+  </si>
+  <si>
+    <t>20142863</t>
+  </si>
+  <si>
+    <t>EWATER LEMON 380</t>
+  </si>
+  <si>
+    <t>20108987</t>
+  </si>
+  <si>
+    <t>V-SOY MULTI-GRAIN200</t>
+  </si>
+  <si>
+    <t>20123171</t>
+  </si>
+  <si>
+    <t>LACTASOY MILK CLG250</t>
+  </si>
+  <si>
+    <t>20135311</t>
+  </si>
+  <si>
+    <t>HYDROPL ISTNC JRK350</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>20142358</t>
+  </si>
+  <si>
+    <t>POWRADE ACTIV WHT400</t>
+  </si>
+  <si>
+    <t>20142359</t>
+  </si>
+  <si>
+    <t>POWRADE ISOTN BLU400</t>
+  </si>
+  <si>
+    <t>20138837</t>
+  </si>
+  <si>
+    <t>MZONE COCO BOOST 500</t>
+  </si>
+  <si>
+    <t>20094167</t>
+  </si>
+  <si>
+    <t>MIZONE MOOD UP 500</t>
+  </si>
+  <si>
+    <t>20094164</t>
+  </si>
+  <si>
+    <t>MIZONE ACTIVE 500ML</t>
+  </si>
+  <si>
+    <t>20141600</t>
+  </si>
+  <si>
+    <t>IDM ISOTONC FRUIT350</t>
+  </si>
+  <si>
+    <t>20141601</t>
+  </si>
+  <si>
+    <t>IDM ISOTONC LYCHE350</t>
+  </si>
+  <si>
+    <t>20065248</t>
+  </si>
+  <si>
+    <t>ION WATER BTL 350ML</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>20118832</t>
+  </si>
+  <si>
+    <t>ION WATER BTL 500ML</t>
+  </si>
+  <si>
+    <t>20015838</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 350ML</t>
+  </si>
+  <si>
+    <t>20009722</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 500ML</t>
+  </si>
+  <si>
+    <t>20038777</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 900ML</t>
+  </si>
+  <si>
+    <t>20019674</t>
+  </si>
+  <si>
+    <t>YOU C1000 ORG WTR500</t>
+  </si>
+  <si>
+    <t>20019673</t>
+  </si>
+  <si>
+    <t>YOU C1000 LMN WTR500</t>
+  </si>
+  <si>
+    <t>20057867</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 500ML</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>20119876</t>
+  </si>
+  <si>
+    <t>HYDR.COCO VITA-D 330</t>
+  </si>
+  <si>
+    <t>20018435</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 250ML</t>
+  </si>
+  <si>
+    <t>20115548</t>
+  </si>
+  <si>
+    <t>IDM COCONUT WTR 250</t>
+  </si>
+  <si>
+    <t>20089821</t>
+  </si>
+  <si>
+    <t>ORONAMIN C DRINK 120</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20115549</t>
+  </si>
+  <si>
+    <t>FIBE MINI 100ML</t>
+  </si>
+  <si>
+    <t>20142467</t>
+  </si>
+  <si>
+    <t>FIT ME UP RLX 160</t>
+  </si>
+  <si>
+    <t>20141124</t>
+  </si>
+  <si>
+    <t>REGEN ORANGE 300ML</t>
+  </si>
+  <si>
+    <t>20139550</t>
+  </si>
+  <si>
+    <t>REGEN LMN LIME 300ML</t>
+  </si>
+  <si>
+    <t>20009737</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK ORG140</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>10039897</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK LMN140</t>
+  </si>
+  <si>
+    <t>20032519</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK APL140</t>
+  </si>
+  <si>
+    <t>20115636</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK MGO140</t>
+  </si>
+  <si>
+    <t>20113135</t>
+  </si>
+  <si>
+    <t>AMUNIZER BTL 140ML</t>
+  </si>
+  <si>
+    <t>20048546</t>
+  </si>
+  <si>
+    <t>HEMAVITON C1000 330</t>
+  </si>
+  <si>
+    <t>20103178</t>
+  </si>
+  <si>
+    <t>HMVTON C1000 LSO 330</t>
+  </si>
+  <si>
+    <t>20103368</t>
+  </si>
+  <si>
+    <t>HMVTON C1000 LMN 330</t>
+  </si>
+  <si>
+    <t>20128794</t>
+  </si>
+  <si>
+    <t>NS/GOODNES KURMA 189</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>20103718</t>
+  </si>
+  <si>
+    <t>TJH KURMA SUSU KR189</t>
+  </si>
+  <si>
+    <t>20124409</t>
+  </si>
+  <si>
+    <t>INDOMLK STRL HNY 189</t>
+  </si>
+  <si>
+    <t>20136193</t>
+  </si>
+  <si>
+    <t>SO GOOD SUSU STRL189</t>
+  </si>
+  <si>
+    <t>20133805</t>
+  </si>
+  <si>
+    <t>ENTRSL OLIVE STRL180</t>
+  </si>
+  <si>
+    <t>20134968</t>
+  </si>
+  <si>
+    <t>COLLAGENA STERIL189</t>
+  </si>
+  <si>
+    <t>20140174</t>
+  </si>
+  <si>
+    <t>BEAR BRAND CLGEN 189</t>
+  </si>
+  <si>
+    <t>10004906</t>
+  </si>
+  <si>
+    <t>BEAR BRAND STERIL189</t>
+  </si>
+  <si>
+    <t>20136952</t>
+  </si>
+  <si>
+    <t>V-SOY SOYA BEAN 300</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>20048096</t>
+  </si>
+  <si>
+    <t>20038726</t>
+  </si>
+  <si>
+    <t>NARAYA KDLAI BTL320</t>
+  </si>
+  <si>
+    <t>20107748</t>
+  </si>
+  <si>
+    <t>MILKU SUSU CKLT 200</t>
+  </si>
+  <si>
+    <t>20107749</t>
+  </si>
+  <si>
+    <t>MILKU SUSU STRO 200</t>
+  </si>
+  <si>
+    <t>20141102</t>
+  </si>
+  <si>
+    <t>MILKU UHT MARIE 200</t>
+  </si>
+  <si>
+    <t>20134047</t>
+  </si>
+  <si>
+    <t>MILKU SUSU ORGNAL200</t>
+  </si>
+  <si>
+    <t>10003373</t>
+  </si>
+  <si>
+    <t>INDOMILK CAIR CHO190</t>
+  </si>
+  <si>
+    <t>10003426</t>
+  </si>
+  <si>
+    <t>INDOMILK CAIR STW190</t>
+  </si>
+  <si>
+    <t>10004443</t>
+  </si>
+  <si>
+    <t>INDOMILK UHT CKL 180</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>10004442</t>
+  </si>
+  <si>
+    <t>INDOMLK UHT STRW 180</t>
+  </si>
+  <si>
+    <t>20070569</t>
+  </si>
+  <si>
+    <t>INDOMLK BANANA 180</t>
+  </si>
+  <si>
+    <t>20134956</t>
+  </si>
+  <si>
+    <t>INDOMILK GOGUMA 180</t>
+  </si>
+  <si>
+    <t>20127735</t>
+  </si>
+  <si>
+    <t>INDMLK DLGNA COFF180</t>
+  </si>
+  <si>
+    <t>20125062</t>
+  </si>
+  <si>
+    <t>INDOMLK KR.BNANA 180</t>
+  </si>
+  <si>
+    <t>20132659</t>
+  </si>
+  <si>
+    <t>INDOMLK HK LYCHEE180</t>
+  </si>
+  <si>
+    <t>20091807</t>
+  </si>
+  <si>
+    <t>DIAMOND UHT CKLT 200</t>
+  </si>
+  <si>
+    <t>20136644</t>
+  </si>
+  <si>
+    <t>DIAMOND UHT MARSM200</t>
+  </si>
+  <si>
+    <t>20137977</t>
+  </si>
+  <si>
+    <t>DIAMOND UHT BBLGM200</t>
+  </si>
+  <si>
+    <t>20019179</t>
+  </si>
+  <si>
+    <t>B/BRAND GOLD MALT140</t>
+  </si>
+  <si>
+    <t>20032643</t>
+  </si>
+  <si>
+    <t>ULTRA LOW FAT COK250</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>20032644</t>
+  </si>
+  <si>
+    <t>ULTRA LOW FAT PLN250</t>
+  </si>
+  <si>
+    <t>20130186</t>
+  </si>
+  <si>
+    <t>GRNFLD UHT CHOCO 250</t>
+  </si>
+  <si>
+    <t>20118209</t>
+  </si>
+  <si>
+    <t>GRNFLD UHT STRAW 250</t>
+  </si>
+  <si>
+    <t>20087413</t>
+  </si>
+  <si>
+    <t>GRNFLD UHT F.CRM 250</t>
+  </si>
+  <si>
+    <t>20138916</t>
+  </si>
+  <si>
+    <t>CIMORY THAI TEA 250</t>
+  </si>
+  <si>
+    <t>20136951</t>
+  </si>
+  <si>
+    <t>CMORY UHT MATCHA 250</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20140795</t>
+  </si>
+  <si>
+    <t>CIMORY UHT CHOCO 225</t>
+  </si>
+  <si>
+    <t>20140794</t>
+  </si>
+  <si>
+    <t>CIMORY UHT MARIE 225</t>
+  </si>
+  <si>
+    <t>20140793</t>
+  </si>
+  <si>
+    <t>CIMORY UHT MTCHA 225</t>
+  </si>
+  <si>
+    <t>20122822</t>
+  </si>
+  <si>
+    <t>CMORY UHT MARIE 250</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>20115187</t>
+  </si>
+  <si>
+    <t>CMORY UHT HZLNUT 250</t>
+  </si>
+  <si>
+    <t>20115188</t>
+  </si>
+  <si>
+    <t>CMORY UHT ALMND 250</t>
+  </si>
+  <si>
+    <t>20104637</t>
+  </si>
+  <si>
+    <t>CIMORY UHT CSHEW 250</t>
+  </si>
+  <si>
+    <t>20099571</t>
+  </si>
+  <si>
+    <t>CIMORY UHT CHOCO 250</t>
+  </si>
+  <si>
+    <t>20104636</t>
+  </si>
+  <si>
+    <t>CIMORY UHT CHOML 250</t>
+  </si>
+  <si>
+    <t>20129109</t>
+  </si>
+  <si>
+    <t>CIMORY CHO.TRMSU 250</t>
+  </si>
+  <si>
+    <t>20099572</t>
+  </si>
+  <si>
+    <t>CIMORY UHT STRAW 250</t>
+  </si>
+  <si>
+    <t>20134390</t>
+  </si>
+  <si>
+    <t>CIMORY BBS LKTSA 250</t>
+  </si>
+  <si>
+    <t>20025753</t>
+  </si>
+  <si>
+    <t>F/F L/FAT COK TPK225</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>20088875</t>
+  </si>
+  <si>
+    <t>FF SWT.DLGHT TPK 225</t>
+  </si>
+  <si>
+    <t>20070253</t>
+  </si>
+  <si>
+    <t>FF COCONUT TPK 225ML</t>
+  </si>
+  <si>
+    <t>20034079</t>
+  </si>
+  <si>
+    <t>F/FLAG COKLT TPK 225</t>
+  </si>
+  <si>
+    <t>20034078</t>
+  </si>
+  <si>
+    <t>F/FLAG STRWB TPK 225</t>
+  </si>
+  <si>
+    <t>20034077</t>
+  </si>
+  <si>
+    <t>F/F FULL CRM TPK 225</t>
+  </si>
+  <si>
+    <t>20128754</t>
+  </si>
+  <si>
+    <t>FF SS.SEREAL CKL 225</t>
+  </si>
+  <si>
+    <t>20136769</t>
+  </si>
+  <si>
+    <t>F.FLAG UHT BERIS 225</t>
+  </si>
+  <si>
+    <t>20136768</t>
+  </si>
+  <si>
+    <t>F.FLAG UHT MATCH 225</t>
+  </si>
+  <si>
+    <t>20142233</t>
+  </si>
+  <si>
+    <t>INDOMILK JAPANE M180</t>
+  </si>
+  <si>
+    <t>10004669</t>
+  </si>
+  <si>
+    <t>ULTRA UHT CHOCO 250M</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>10004668</t>
+  </si>
+  <si>
+    <t>ULTRA UHT STRAW 250M</t>
+  </si>
+  <si>
+    <t>10004676</t>
+  </si>
+  <si>
+    <t>ULTRA PLAIN SLIM250M</t>
+  </si>
+  <si>
+    <t>10007380</t>
+  </si>
+  <si>
+    <t>ULTRA SLIM COKLAT200</t>
+  </si>
+  <si>
+    <t>10008095</t>
+  </si>
+  <si>
+    <t>ULTRA SLIM STRAW 200</t>
+  </si>
+  <si>
+    <t>10007379</t>
+  </si>
+  <si>
+    <t>ULTRA SLIM PLAIN 200</t>
+  </si>
+  <si>
+    <t>20090189</t>
+  </si>
+  <si>
+    <t>ULTRA SUSU KRML 200</t>
+  </si>
+  <si>
+    <t>20088964</t>
+  </si>
+  <si>
+    <t>ULTRA SUSU TARO 200</t>
+  </si>
+  <si>
+    <t>20138895</t>
+  </si>
+  <si>
+    <t>ULTRA UHT BLUBRY 200</t>
+  </si>
+  <si>
+    <t>20110968</t>
+  </si>
+  <si>
+    <t>MUJIGAE BNNA MLK 250</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>20110967</t>
+  </si>
+  <si>
+    <t>MUJIGAE CHOC BAN 250</t>
+  </si>
+  <si>
+    <t>20126897</t>
+  </si>
+  <si>
+    <t>MUJIGAE STRW BAN 250</t>
+  </si>
+  <si>
+    <t>20138050</t>
+  </si>
+  <si>
+    <t>MUJIGAE WTRMLN 250</t>
+  </si>
+  <si>
+    <t>20130518</t>
+  </si>
+  <si>
+    <t>TS ALMND.CHOCO 190ML</t>
+  </si>
+  <si>
+    <t>20118377</t>
+  </si>
+  <si>
+    <t>TS OAT VANILLA 190ML</t>
+  </si>
+  <si>
+    <t>20139295</t>
+  </si>
+  <si>
+    <t>BROOKFARM ORI 200ML</t>
+  </si>
+  <si>
+    <t>20139300</t>
+  </si>
+  <si>
+    <t>BROOKFARM MATCHA 200</t>
+  </si>
+  <si>
+    <t>20037974</t>
+  </si>
+  <si>
+    <t>ULTRA UHT MOKA 250</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>20139359</t>
+  </si>
+  <si>
+    <t>KIT KAT CHO KLG 220</t>
+  </si>
+  <si>
+    <t>10014404</t>
+  </si>
+  <si>
+    <t>MILO HEALTY DRINK220</t>
+  </si>
+  <si>
+    <t>20037607</t>
+  </si>
+  <si>
+    <t>MILO DRINK KLG 220ML</t>
+  </si>
+  <si>
+    <t>20135340</t>
+  </si>
+  <si>
+    <t>MILO DRNK EXT.CHO220</t>
+  </si>
+  <si>
+    <t>20136206</t>
+  </si>
+  <si>
+    <t>MILO DRNK COOL 220</t>
+  </si>
+  <si>
+    <t>20139358</t>
+  </si>
+  <si>
+    <t>MILO PRO UHT 225ML</t>
+  </si>
+  <si>
+    <t>20019597</t>
+  </si>
+  <si>
+    <t>MILO ACTIV-GO 180ML</t>
+  </si>
+  <si>
+    <t>20133873</t>
+  </si>
+  <si>
+    <t>MILO CHOCO BANANA180</t>
+  </si>
+  <si>
+    <t>20133871</t>
+  </si>
+  <si>
+    <t>MILO CHOCO CEREAL180</t>
+  </si>
+  <si>
+    <t>20047247</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL 750</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>20008767</t>
+  </si>
+  <si>
+    <t>CLUB AIR MNRAL 600ML</t>
+  </si>
+  <si>
+    <t>20090527</t>
+  </si>
+  <si>
+    <t>CRYSTALIN BTL 600mL</t>
+  </si>
+  <si>
+    <t>20077499</t>
+  </si>
+  <si>
+    <t>PRISTINE 8.6+ BTL600</t>
+  </si>
+  <si>
+    <t>20139699</t>
+  </si>
+  <si>
+    <t>OASIS  MNRL PH9 500</t>
+  </si>
+  <si>
+    <t>20061938</t>
+  </si>
+  <si>
+    <t>SUPER O2 SPRTVO 600</t>
+  </si>
+  <si>
+    <t>20056219</t>
+  </si>
+  <si>
+    <t>ETERNALPLUS BTL 500</t>
+  </si>
+  <si>
+    <t>20045052</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR MIN330</t>
+  </si>
+  <si>
+    <t>PT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>10015532</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL 330</t>
+  </si>
+  <si>
+    <t>20137991</t>
+  </si>
+  <si>
+    <t>AQUVIVA BTL 700ML</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>20037131</t>
+  </si>
+  <si>
+    <t>PRIM-A AIR MNRAL 600</t>
+  </si>
+  <si>
+    <t>20142495</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR MIN 1L</t>
+  </si>
+  <si>
+    <t>20069208</t>
+  </si>
+  <si>
+    <t>LE MINERALE 600ML</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>10003814</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL 600</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>10004336</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR MIN600</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>PT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20089542</t>
+  </si>
+  <si>
+    <t>IDM AIR MN 8+ BTL500</t>
+  </si>
+  <si>
+    <t>RT,(E-15H)</t>
+  </si>
+  <si>
+    <t>20052629</t>
+  </si>
+  <si>
+    <t>IDM AIR DGN OKSGN600</t>
+  </si>
+  <si>
+    <t>PT,(E-15H)</t>
+  </si>
+  <si>
+    <t>20005529</t>
+  </si>
+  <si>
+    <t>NESTLE PURE LIFE 600</t>
+  </si>
+  <si>
     <t>20138035</t>
   </si>
   <si>
     <t>CAFFINO OATMARIE 200</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20078206</t>
-  </si>
-  <si>
-    <t>LUWAK WHT ORGL 220ML</t>
-  </si>
-  <si>
-    <t>20076770</t>
-  </si>
-  <si>
-    <t>G/DAY CAPPUCCINO 230</t>
-  </si>
-  <si>
-    <t>20045674</t>
-  </si>
-  <si>
-    <t>G/DAY F.MOCACINO 230</t>
-  </si>
-  <si>
-    <t>20045673</t>
-  </si>
-  <si>
-    <t>G/DAY TIRAMISU/B 230</t>
-  </si>
-  <si>
-    <t>20056193</t>
-  </si>
-  <si>
-    <t>GOOD DAY AVCDO/D 230</t>
-  </si>
-  <si>
-    <t>20132329</t>
-  </si>
-  <si>
-    <t>GOOD DAY GRVY CKS230</t>
-  </si>
-  <si>
-    <t>20134557</t>
-  </si>
-  <si>
-    <t>OATSIDE CRML MCHT200</t>
-  </si>
-  <si>
-    <t>20129108</t>
-  </si>
-  <si>
-    <t>OATSDE COFFEE 200ML</t>
-  </si>
-  <si>
-    <t>20142499</t>
-  </si>
-  <si>
-    <t>OATSDE ESPR RST 240</t>
-  </si>
-  <si>
-    <t>20139577</t>
-  </si>
-  <si>
-    <t>PC AREN LATTE 210ML</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139578</t>
-  </si>
-  <si>
-    <t>PC GOLDN CARAMEL 210</t>
-  </si>
-  <si>
-    <t>20139576</t>
-  </si>
-  <si>
-    <t>PC CRMY CPUCCINO 210</t>
-  </si>
-  <si>
-    <t>20142601</t>
-  </si>
-  <si>
-    <t>NSCAFE MTCHA ESP 220</t>
-  </si>
-  <si>
-    <t>20140431</t>
-  </si>
-  <si>
-    <t>NSCAFE KITKAT LAT220</t>
-  </si>
-  <si>
-    <t>20133058</t>
-  </si>
-  <si>
-    <t>NSCAFE OAT LATTE 220</t>
-  </si>
-  <si>
-    <t>20027768</t>
-  </si>
-  <si>
-    <t>NESCAFE COFF CRM 180</t>
-  </si>
-  <si>
-    <t>20114494</t>
-  </si>
-  <si>
-    <t>NSCAFE CRML MCTO 220</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20114495</t>
-  </si>
-  <si>
-    <t>NESCAFE CPUCCINO 220</t>
-  </si>
-  <si>
-    <t>20114493</t>
-  </si>
-  <si>
-    <t>NESCAFE LATTE 220ML</t>
-  </si>
-  <si>
-    <t>20138057</t>
-  </si>
-  <si>
-    <t>NSCAFE GULA AREN 220</t>
-  </si>
-  <si>
-    <t>20121456</t>
-  </si>
-  <si>
-    <t>NSCAFE ICE BLACK 220</t>
-  </si>
-  <si>
-    <t>20000787</t>
-  </si>
-  <si>
-    <t>NESCAFE ICE.CF OR220</t>
-  </si>
-  <si>
-    <t>20014954</t>
-  </si>
-  <si>
-    <t>NESCAFE ICE.CF MC220</t>
-  </si>
-  <si>
-    <t>20000786</t>
-  </si>
-  <si>
-    <t>NESCAFE ICE.CF LT220</t>
-  </si>
-  <si>
-    <t>20125115</t>
-  </si>
-  <si>
-    <t>STARBUCKS LATTE 220</t>
-  </si>
-  <si>
-    <t>20125126</t>
-  </si>
-  <si>
-    <t>STARBUCKS CARAMEL220</t>
-  </si>
-  <si>
-    <t>20014608</t>
-  </si>
-  <si>
-    <t>HRMVTON PSK BUMI 150</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>10006263</t>
-  </si>
-  <si>
-    <t>HEMAVITON ENERGY 150</t>
-  </si>
-  <si>
-    <t>10002602</t>
-  </si>
-  <si>
-    <t>M-150 HEALT DRINK150</t>
-  </si>
-  <si>
-    <t>10002595</t>
-  </si>
-  <si>
-    <t>KRATINGDAENG 150 ML</t>
-  </si>
-  <si>
-    <t>10003427</t>
-  </si>
-  <si>
-    <t>KRATINGDAENG SPR.150</t>
-  </si>
-  <si>
-    <t>20022431</t>
-  </si>
-  <si>
-    <t>RED BULL E/DRNK 250</t>
-  </si>
-  <si>
-    <t>20056989</t>
-  </si>
-  <si>
-    <t>RED BULL GOLD 250ML</t>
-  </si>
-  <si>
-    <t>20138252</t>
-  </si>
-  <si>
-    <t>EXTRA JOSS ULTIMT250</t>
-  </si>
-  <si>
-    <t>20038425</t>
-  </si>
-  <si>
-    <t>NTRIVE/B BLCKRNT 100</t>
-  </si>
-  <si>
-    <t>20071510</t>
-  </si>
-  <si>
-    <t>NTRVE BNCOL LYCH 100</t>
-  </si>
-  <si>
-    <t>20003786</t>
-  </si>
-  <si>
-    <t>NU GREEN TEA HNY 450</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20113059</t>
-  </si>
-  <si>
-    <t>NU YOGURT TEA 450ML</t>
-  </si>
-  <si>
-    <t>20139732</t>
-  </si>
-  <si>
-    <t>NU YOGRT TEA BRY 450</t>
-  </si>
-  <si>
-    <t>20036157</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BOTOL 450</t>
-  </si>
-  <si>
-    <t>20002203</t>
-  </si>
-  <si>
-    <t>SOSRO F.TEA APEL 500</t>
-  </si>
-  <si>
-    <t>20003698</t>
-  </si>
-  <si>
-    <t>SOSRO FR.TEA XTRM500</t>
-  </si>
-  <si>
-    <t>20002205</t>
-  </si>
-  <si>
-    <t>SOSRO F.TEA BLKCR500</t>
-  </si>
-  <si>
-    <t>20134046</t>
-  </si>
-  <si>
-    <t>FRUIT TEA FREEZE 500</t>
-  </si>
-  <si>
-    <t>20126464</t>
-  </si>
-  <si>
-    <t>IDM TEH APL&amp;LYCHE350</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20101897</t>
-  </si>
-  <si>
-    <t>IDM TEH APEL 350ML</t>
-  </si>
-  <si>
-    <t>20132840</t>
-  </si>
-  <si>
-    <t>IDM TEH BLCKCRRNT350</t>
-  </si>
-  <si>
-    <t>20066454</t>
-  </si>
-  <si>
-    <t>FRUIT TEA BLCKCR 350</t>
-  </si>
-  <si>
-    <t>20073495</t>
-  </si>
-  <si>
-    <t>FRUIT TEA FREEZE 350</t>
-  </si>
-  <si>
-    <t>20066455</t>
-  </si>
-  <si>
-    <t>FRUIT TEA APPLE 350</t>
-  </si>
-  <si>
-    <t>20079972</t>
-  </si>
-  <si>
-    <t>FRUIT TEA MRKISA 350</t>
-  </si>
-  <si>
-    <t>20138841</t>
-  </si>
-  <si>
-    <t>POKKA NAT. H.ORG 350</t>
-  </si>
-  <si>
-    <t>20135619</t>
-  </si>
-  <si>
-    <t>TEBS ZERO LYCHEE 300</t>
-  </si>
-  <si>
-    <t>20060207</t>
-  </si>
-  <si>
-    <t>I/OCHA TEH MLATI 350</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20048934</t>
-  </si>
-  <si>
-    <t>I/OCHA GRN TEA 350ML</t>
-  </si>
-  <si>
-    <t>20142077</t>
-  </si>
-  <si>
-    <t>TEH LEMON MADU 350ML</t>
-  </si>
-  <si>
-    <t>20018904</t>
-  </si>
-  <si>
-    <t>NU GREEN TEA HNY 330</t>
-  </si>
-  <si>
-    <t>20053867</t>
-  </si>
-  <si>
-    <t>TEH GELAS BTL 350ML</t>
-  </si>
-  <si>
-    <t>20073396</t>
-  </si>
-  <si>
-    <t>S-TEE BTL 390ML</t>
-  </si>
-  <si>
-    <t>20072249</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BOTOL 350</t>
-  </si>
-  <si>
-    <t>20122278</t>
-  </si>
-  <si>
-    <t>TEH BOTOL LS.SGR 350</t>
-  </si>
-  <si>
-    <t>20082395</t>
-  </si>
-  <si>
-    <t>TEH BOTOL TAWAR 350</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20048155</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR350</t>
-  </si>
-  <si>
-    <t>20037565</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI500</t>
-  </si>
-  <si>
-    <t>20048348</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR500</t>
-  </si>
-  <si>
-    <t>10036640</t>
-  </si>
-  <si>
-    <t>TEH KOTAK JASMINE300</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20048435</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LESS/S 300</t>
-  </si>
-  <si>
-    <t>20143447</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH ORI 300</t>
-  </si>
-  <si>
-    <t>20143446</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR300</t>
-  </si>
-  <si>
-    <t>20044334</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK300</t>
-  </si>
-  <si>
-    <t>10005128</t>
-  </si>
-  <si>
-    <t>SOSRO TEH KOTAK B250</t>
-  </si>
-  <si>
-    <t>20024315</t>
-  </si>
-  <si>
-    <t>TEH BOTOL LS.SGR 250</t>
-  </si>
-  <si>
-    <t>20026226</t>
-  </si>
-  <si>
-    <t>ULTRA TEH KOTAK 500</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20100142</t>
-  </si>
-  <si>
-    <t>TEH KOTAK BLCKCR 300</t>
-  </si>
-  <si>
-    <t>20100143</t>
-  </si>
-  <si>
-    <t>TEH KOTAK APPLE 300</t>
-  </si>
-  <si>
-    <t>20137159</t>
-  </si>
-  <si>
-    <t>TEH KOTAK MANGGA 300</t>
-  </si>
-  <si>
-    <t>20087016</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LEMON 300</t>
-  </si>
-  <si>
-    <t>20135647</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LYCHEE 300</t>
-  </si>
-  <si>
-    <t>20117687</t>
-  </si>
-  <si>
-    <t>DLMNT BOBA MTCHA 240</t>
-  </si>
-  <si>
-    <t>20117682</t>
-  </si>
-  <si>
-    <t>DLMNT BOBA RD.VEL240</t>
-  </si>
-  <si>
-    <t>20080088</t>
-  </si>
-  <si>
-    <t>POKKA GREEN TEA 450</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20036765</t>
-  </si>
-  <si>
-    <t>FRESTEA GRN MADU 500</t>
-  </si>
-  <si>
-    <t>20012574</t>
-  </si>
-  <si>
-    <t>FRESTEA TEH APEL 500</t>
-  </si>
-  <si>
-    <t>20035829</t>
-  </si>
-  <si>
-    <t>TEBS TEA WT/SODA 500</t>
-  </si>
-  <si>
-    <t>20093586</t>
-  </si>
-  <si>
-    <t>ICHTN THAI M.COFF300</t>
-  </si>
-  <si>
-    <t>20136363</t>
-  </si>
-  <si>
-    <t>ICHTN DARK CHOCO 300</t>
-  </si>
-  <si>
-    <t>20135599</t>
-  </si>
-  <si>
-    <t>ICHTAN KRN BANANA300</t>
-  </si>
-  <si>
-    <t>20142025</t>
-  </si>
-  <si>
-    <t>ICHITAN MLN MILK 300</t>
-  </si>
-  <si>
-    <t>20040383</t>
-  </si>
-  <si>
-    <t>NU MILK TEA 330ML</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20069527</t>
-  </si>
-  <si>
-    <t>NU TEH TARIK 330ML</t>
-  </si>
-  <si>
-    <t>20128233</t>
-  </si>
-  <si>
-    <t>NU CHO TEA HZLTEA330</t>
-  </si>
-  <si>
-    <t>20138202</t>
-  </si>
-  <si>
-    <t>NU MATCHA LATTEA 330</t>
-  </si>
-  <si>
-    <t>20141981</t>
-  </si>
-  <si>
-    <t>DUM2 CHO MILK TEA330</t>
-  </si>
-  <si>
-    <t>20141980</t>
-  </si>
-  <si>
-    <t>DUM2 RYL MILK TEA330</t>
-  </si>
-  <si>
-    <t>20085054</t>
-  </si>
-  <si>
-    <t>ICHTN THAI M.TEA 300</t>
-  </si>
-  <si>
-    <t>20101102</t>
-  </si>
-  <si>
-    <t>ICHTN MLK GR.TEA 300</t>
-  </si>
-  <si>
-    <t>20113450</t>
-  </si>
-  <si>
-    <t>ICHITAN MLK BRWN 300</t>
-  </si>
-  <si>
-    <t>20113377</t>
-  </si>
-  <si>
-    <t>FLRDINA COCO BIT 350</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20043877</t>
-  </si>
-  <si>
-    <t>FLORIDINA ORANGE 350</t>
-  </si>
-  <si>
-    <t>20021178</t>
-  </si>
-  <si>
-    <t>MINUTE MAID ORG 300</t>
-  </si>
-  <si>
-    <t>20062818</t>
-  </si>
-  <si>
-    <t>FRUITAMIN LYCHE 350</t>
-  </si>
-  <si>
-    <t>20091654</t>
-  </si>
-  <si>
-    <t>COCO BIT SP.GUAV 350</t>
-  </si>
-  <si>
-    <t>20140331</t>
-  </si>
-  <si>
-    <t>COCO BIT STRAW.S 350</t>
-  </si>
-  <si>
-    <t>20140327</t>
-  </si>
-  <si>
-    <t>COCO BIT KY.GRP 350</t>
-  </si>
-  <si>
-    <t>20140332</t>
-  </si>
-  <si>
-    <t>COCO BIT HOK.MLN 350</t>
-  </si>
-  <si>
-    <t>20042848</t>
-  </si>
-  <si>
-    <t>MOGU MOGU LYCHHE 320</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>20047245</t>
-  </si>
-  <si>
-    <t>MOGU MOGU CCONUT 320</t>
-  </si>
-  <si>
-    <t>20076486</t>
-  </si>
-  <si>
-    <t>MOGU MOGU MELON 320</t>
-  </si>
-  <si>
-    <t>20042859</t>
-  </si>
-  <si>
-    <t>MOGU MOGU MANGGA 320</t>
-  </si>
-  <si>
-    <t>20042860</t>
-  </si>
-  <si>
-    <t>MOGU MOGU STRWBRY320</t>
-  </si>
-  <si>
-    <t>20047244</t>
-  </si>
-  <si>
-    <t>MOGU MOGU GRAPE 320</t>
-  </si>
-  <si>
-    <t>20137095</t>
-  </si>
-  <si>
-    <t>MOGU2 BUBBLE GUM 320</t>
-  </si>
-  <si>
-    <t>20136277</t>
-  </si>
-  <si>
-    <t>SNPRD FRT MG.PINE220</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>20134353</t>
-  </si>
-  <si>
-    <t>IDM S/B NNS&amp;MRKSA220</t>
-  </si>
-  <si>
-    <t>20134354</t>
-  </si>
-  <si>
-    <t>IDM SARI BH NANAS220</t>
-  </si>
-  <si>
-    <t>20089805</t>
-  </si>
-  <si>
-    <t>OLATTE PEACH KLG 240</t>
-  </si>
-  <si>
-    <t>RT,(E-2.5B)</t>
-  </si>
-  <si>
-    <t>20089806</t>
-  </si>
-  <si>
-    <t>OLATTE PEAR KLG 240</t>
-  </si>
-  <si>
-    <t>20135975</t>
-  </si>
-  <si>
-    <t>OLATTE STRWB KLG 240</t>
-  </si>
-  <si>
-    <t>20052734</t>
-  </si>
-  <si>
-    <t>LOTTE MILKIS MLN 250</t>
-  </si>
-  <si>
-    <t>10028190</t>
-  </si>
-  <si>
-    <t>LOTTE MILKIS KLG 250</t>
-  </si>
-  <si>
-    <t>10008887</t>
-  </si>
-  <si>
-    <t>ULTRA KCNG HIJAU 250</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>10000278</t>
-  </si>
-  <si>
-    <t>ABC KACANG HIJAU 250</t>
-  </si>
-  <si>
-    <t>20120929</t>
-  </si>
-  <si>
-    <t>PANDA GR.JLY+BSL 310</t>
-  </si>
-  <si>
-    <t>20046319</t>
-  </si>
-  <si>
-    <t>PANDA GRASS JELY310</t>
-  </si>
-  <si>
-    <t>20141495</t>
-  </si>
-  <si>
-    <t>PANDA GRN GRS JEL310</t>
-  </si>
-  <si>
-    <t>20112383</t>
-  </si>
-  <si>
-    <t>MR.NATA JELI LECI126</t>
-  </si>
-  <si>
-    <t>20112382</t>
-  </si>
-  <si>
-    <t>MR.NATA JEL BLU/B126</t>
-  </si>
-  <si>
-    <t>20136250</t>
-  </si>
-  <si>
-    <t>JELE JELLY LYCHEE150</t>
-  </si>
-  <si>
-    <t>20055762</t>
-  </si>
-  <si>
-    <t>JELE COLLAGEN 150G</t>
-  </si>
-  <si>
-    <t>10007970</t>
-  </si>
-  <si>
-    <t>BUAVITA JAMBU SL 245</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>10007974</t>
-  </si>
-  <si>
-    <t>BUAVITA LYCHEE SL245</t>
-  </si>
-  <si>
-    <t>10007971</t>
-  </si>
-  <si>
-    <t>BUAVITA ORANGE SL245</t>
-  </si>
-  <si>
-    <t>10007973</t>
-  </si>
-  <si>
-    <t>BUAVITA MANGGA 245ML</t>
-  </si>
-  <si>
-    <t>10007972</t>
-  </si>
-  <si>
-    <t>BUAVITA JC APPLE 245</t>
-  </si>
-  <si>
-    <t>20140324</t>
-  </si>
-  <si>
-    <t>BUAVITA K.STRAW 245</t>
-  </si>
-  <si>
-    <t>20140328</t>
-  </si>
-  <si>
-    <t>BUAVITA K MS.GRP 245</t>
-  </si>
-  <si>
-    <t>10007385</t>
-  </si>
-  <si>
-    <t>ULTRA SR ASAM SLM250</t>
-  </si>
-  <si>
-    <t>20136649</t>
-  </si>
-  <si>
-    <t>DIAMOND JC CRANBR200</t>
-  </si>
-  <si>
-    <t>20065041</t>
-  </si>
-  <si>
-    <t>PORORO BLUEBERY235ML</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>20037137</t>
-  </si>
-  <si>
-    <t>PORORO STROBRI 235ML</t>
-  </si>
-  <si>
-    <t>20037136</t>
-  </si>
-  <si>
-    <t>PORORO SUSU 235ML</t>
-  </si>
-  <si>
-    <t>20085010</t>
-  </si>
-  <si>
-    <t>PORORO MANGO 235</t>
-  </si>
-  <si>
-    <t>20137094</t>
-  </si>
-  <si>
-    <t>PORORO PEACH 235</t>
-  </si>
-  <si>
-    <t>20141361</t>
-  </si>
-  <si>
-    <t>PORORO ZERO STRW 235</t>
-  </si>
-  <si>
-    <t>20141360</t>
-  </si>
-  <si>
-    <t>PORORO ZERO MILK 235</t>
-  </si>
-  <si>
-    <t>20129123</t>
-  </si>
-  <si>
-    <t>OATSDE CHOCO 200</t>
-  </si>
-  <si>
-    <t>20129102</t>
-  </si>
-  <si>
-    <t>OATSDE BR.BLEND 200</t>
-  </si>
-  <si>
-    <t>20069773</t>
-  </si>
-  <si>
-    <t>ISOPLUS BTL 350ML</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>20128918</t>
-  </si>
-  <si>
-    <t>ISOPLUS COCO 350ML</t>
-  </si>
-  <si>
-    <t>20138959</t>
-  </si>
-  <si>
-    <t>IF COCONUT WTR 350ML</t>
-  </si>
-  <si>
-    <t>20142818</t>
-  </si>
-  <si>
-    <t>EWATER GRAPEFRT 555</t>
-  </si>
-  <si>
-    <t>20142819</t>
-  </si>
-  <si>
-    <t>EWATER LEMON 555ML</t>
-  </si>
-  <si>
-    <t>20142862</t>
-  </si>
-  <si>
-    <t>EWATER GRPFRT 380</t>
-  </si>
-  <si>
-    <t>20142863</t>
-  </si>
-  <si>
-    <t>EWATER LEMON 380</t>
-  </si>
-  <si>
-    <t>20108987</t>
-  </si>
-  <si>
-    <t>V-SOY MULTI-GRAIN200</t>
-  </si>
-  <si>
-    <t>20123171</t>
-  </si>
-  <si>
-    <t>LACTASOY MILK CLG250</t>
-  </si>
-  <si>
-    <t>20135311</t>
-  </si>
-  <si>
-    <t>HYDROPL ISTNC JRK350</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>20142358</t>
-  </si>
-  <si>
-    <t>POWRADE ACTIV WHT400</t>
-  </si>
-  <si>
-    <t>20142359</t>
-  </si>
-  <si>
-    <t>POWRADE ISOTN BLU400</t>
-  </si>
-  <si>
-    <t>20138837</t>
-  </si>
-  <si>
-    <t>MZONE COCO BOOST 500</t>
-  </si>
-  <si>
-    <t>20094167</t>
-  </si>
-  <si>
-    <t>MIZONE MOOD UP 500</t>
-  </si>
-  <si>
-    <t>20094164</t>
-  </si>
-  <si>
-    <t>MIZONE ACTIVE 500ML</t>
-  </si>
-  <si>
-    <t>20141600</t>
-  </si>
-  <si>
-    <t>IDM ISOTONC FRUIT350</t>
-  </si>
-  <si>
-    <t>20141601</t>
-  </si>
-  <si>
-    <t>IDM ISOTONC LYCHE350</t>
-  </si>
-  <si>
-    <t>20065248</t>
-  </si>
-  <si>
-    <t>ION WATER BTL 350ML</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>20118832</t>
-  </si>
-  <si>
-    <t>ION WATER BTL 500ML</t>
-  </si>
-  <si>
-    <t>20015838</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 350ML</t>
-  </si>
-  <si>
-    <t>20009722</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 500ML</t>
-  </si>
-  <si>
-    <t>20038777</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 900ML</t>
-  </si>
-  <si>
-    <t>20019674</t>
-  </si>
-  <si>
-    <t>YOU C1000 ORG WTR500</t>
-  </si>
-  <si>
-    <t>20019673</t>
-  </si>
-  <si>
-    <t>YOU C1000 LMN WTR500</t>
-  </si>
-  <si>
-    <t>20057867</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 500ML</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>20119876</t>
-  </si>
-  <si>
-    <t>HYDR.COCO VITA-D 330</t>
-  </si>
-  <si>
-    <t>20018435</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 250ML</t>
-  </si>
-  <si>
-    <t>20115548</t>
-  </si>
-  <si>
-    <t>IDM COCONUT WTR 250</t>
-  </si>
-  <si>
-    <t>20089821</t>
-  </si>
-  <si>
-    <t>ORONAMIN C DRINK 120</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20115549</t>
-  </si>
-  <si>
-    <t>FIBE MINI 100ML</t>
-  </si>
-  <si>
-    <t>20142467</t>
-  </si>
-  <si>
-    <t>FIT ME UP RLX 160</t>
-  </si>
-  <si>
-    <t>20141124</t>
-  </si>
-  <si>
-    <t>REGEN ORANGE 300ML</t>
-  </si>
-  <si>
-    <t>20139550</t>
-  </si>
-  <si>
-    <t>REGEN LMN LIME 300ML</t>
-  </si>
-  <si>
-    <t>20009737</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK ORG140</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>10039897</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK LMN140</t>
-  </si>
-  <si>
-    <t>20032519</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK APL140</t>
-  </si>
-  <si>
-    <t>20115636</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK MGO140</t>
-  </si>
-  <si>
-    <t>20113135</t>
-  </si>
-  <si>
-    <t>AMUNIZER BTL 140ML</t>
-  </si>
-  <si>
-    <t>20048546</t>
-  </si>
-  <si>
-    <t>HEMAVITON C1000 330</t>
-  </si>
-  <si>
-    <t>20103178</t>
-  </si>
-  <si>
-    <t>HMVTON C1000 LSO 330</t>
-  </si>
-  <si>
-    <t>20103368</t>
-  </si>
-  <si>
-    <t>HMVTON C1000 LMN 330</t>
-  </si>
-  <si>
-    <t>20128794</t>
-  </si>
-  <si>
-    <t>NS/GOODNES KURMA 189</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>20103718</t>
-  </si>
-  <si>
-    <t>TJH KURMA SUSU KR189</t>
-  </si>
-  <si>
-    <t>20124409</t>
-  </si>
-  <si>
-    <t>INDOMLK STRL HNY 189</t>
-  </si>
-  <si>
-    <t>20136193</t>
-  </si>
-  <si>
-    <t>SO GOOD SUSU STRL189</t>
-  </si>
-  <si>
-    <t>20133805</t>
-  </si>
-  <si>
-    <t>ENTRSL OLIVE STRL180</t>
-  </si>
-  <si>
-    <t>20134968</t>
-  </si>
-  <si>
-    <t>COLLAGENA STERIL189</t>
-  </si>
-  <si>
-    <t>20140174</t>
-  </si>
-  <si>
-    <t>BEAR BRAND CLGEN 189</t>
-  </si>
-  <si>
-    <t>10004906</t>
-  </si>
-  <si>
-    <t>BEAR BRAND STERIL189</t>
-  </si>
-  <si>
-    <t>20136952</t>
-  </si>
-  <si>
-    <t>V-SOY SOYA BEAN 300</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>20048096</t>
-  </si>
-  <si>
-    <t>20038726</t>
-  </si>
-  <si>
-    <t>NARAYA KDLAI BTL320</t>
-  </si>
-  <si>
-    <t>20107748</t>
-  </si>
-  <si>
-    <t>MILKU SUSU CKLT 200</t>
-  </si>
-  <si>
-    <t>20107749</t>
-  </si>
-  <si>
-    <t>MILKU SUSU STRO 200</t>
-  </si>
-  <si>
-    <t>20141102</t>
-  </si>
-  <si>
-    <t>MILKU UHT MARIE 200</t>
-  </si>
-  <si>
-    <t>20134047</t>
-  </si>
-  <si>
-    <t>MILKU SUSU ORGNAL200</t>
-  </si>
-  <si>
-    <t>10003373</t>
-  </si>
-  <si>
-    <t>INDOMILK CAIR CHO190</t>
-  </si>
-  <si>
-    <t>10003426</t>
-  </si>
-  <si>
-    <t>INDOMILK CAIR STW190</t>
-  </si>
-  <si>
-    <t>10004443</t>
-  </si>
-  <si>
-    <t>INDOMILK UHT CKL 180</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>10004442</t>
-  </si>
-  <si>
-    <t>INDOMLK UHT STRW 180</t>
-  </si>
-  <si>
-    <t>20070569</t>
-  </si>
-  <si>
-    <t>INDOMLK BANANA 180</t>
-  </si>
-  <si>
-    <t>20134956</t>
-  </si>
-  <si>
-    <t>INDOMILK GOGUMA 180</t>
-  </si>
-  <si>
-    <t>20127735</t>
-  </si>
-  <si>
-    <t>INDMLK DLGNA COFF180</t>
-  </si>
-  <si>
-    <t>20125062</t>
-  </si>
-  <si>
-    <t>INDOMLK KR.BNANA 180</t>
-  </si>
-  <si>
-    <t>20132659</t>
-  </si>
-  <si>
-    <t>INDOMLK HK LYCHEE180</t>
-  </si>
-  <si>
-    <t>20091807</t>
-  </si>
-  <si>
-    <t>DIAMOND UHT CKLT 200</t>
-  </si>
-  <si>
-    <t>20136644</t>
-  </si>
-  <si>
-    <t>DIAMOND UHT MARSM200</t>
-  </si>
-  <si>
-    <t>20137977</t>
-  </si>
-  <si>
-    <t>DIAMOND UHT BBLGM200</t>
-  </si>
-  <si>
-    <t>20019179</t>
-  </si>
-  <si>
-    <t>B/BRAND GOLD MALT140</t>
-  </si>
-  <si>
-    <t>20032643</t>
-  </si>
-  <si>
-    <t>ULTRA LOW FAT COK250</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>20032644</t>
-  </si>
-  <si>
-    <t>ULTRA LOW FAT PLN250</t>
-  </si>
-  <si>
-    <t>20130186</t>
-  </si>
-  <si>
-    <t>GRNFLD UHT CHOCO 250</t>
-  </si>
-  <si>
-    <t>20118209</t>
-  </si>
-  <si>
-    <t>GRNFLD UHT STRAW 250</t>
-  </si>
-  <si>
-    <t>20087413</t>
-  </si>
-  <si>
-    <t>GRNFLD UHT F.CRM 250</t>
-  </si>
-  <si>
-    <t>20138916</t>
-  </si>
-  <si>
-    <t>CIMORY THAI TEA 250</t>
-  </si>
-  <si>
-    <t>20136951</t>
-  </si>
-  <si>
-    <t>CMORY UHT MATCHA 250</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20140795</t>
-  </si>
-  <si>
-    <t>CIMORY UHT CHOCO 225</t>
-  </si>
-  <si>
-    <t>20140794</t>
-  </si>
-  <si>
-    <t>CIMORY UHT MARIE 225</t>
-  </si>
-  <si>
-    <t>20140793</t>
-  </si>
-  <si>
-    <t>CIMORY UHT MTCHA 225</t>
-  </si>
-  <si>
-    <t>20122822</t>
-  </si>
-  <si>
-    <t>CMORY UHT MARIE 250</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>20115187</t>
-  </si>
-  <si>
-    <t>CMORY UHT HZLNUT 250</t>
-  </si>
-  <si>
-    <t>20115188</t>
-  </si>
-  <si>
-    <t>CMORY UHT ALMND 250</t>
-  </si>
-  <si>
-    <t>20104637</t>
-  </si>
-  <si>
-    <t>CIMORY UHT CSHEW 250</t>
-  </si>
-  <si>
-    <t>20099571</t>
-  </si>
-  <si>
-    <t>CIMORY UHT CHOCO 250</t>
-  </si>
-  <si>
-    <t>20104636</t>
-  </si>
-  <si>
-    <t>CIMORY UHT CHOML 250</t>
-  </si>
-  <si>
-    <t>20129109</t>
-  </si>
-  <si>
-    <t>CIMORY CHO.TRMSU 250</t>
-  </si>
-  <si>
-    <t>20099572</t>
-  </si>
-  <si>
-    <t>CIMORY UHT STRAW 250</t>
-  </si>
-  <si>
-    <t>20134390</t>
-  </si>
-  <si>
-    <t>CIMORY BBS LKTSA 250</t>
-  </si>
-  <si>
-    <t>20025753</t>
-  </si>
-  <si>
-    <t>F/F L/FAT COK TPK225</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>20088875</t>
-  </si>
-  <si>
-    <t>FF SWT.DLGHT TPK 225</t>
-  </si>
-  <si>
-    <t>20070253</t>
-  </si>
-  <si>
-    <t>FF COCONUT TPK 225ML</t>
-  </si>
-  <si>
-    <t>20034079</t>
-  </si>
-  <si>
-    <t>F/FLAG COKLT TPK 225</t>
-  </si>
-  <si>
-    <t>20034078</t>
-  </si>
-  <si>
-    <t>F/FLAG STRWB TPK 225</t>
-  </si>
-  <si>
-    <t>20034077</t>
-  </si>
-  <si>
-    <t>F/F FULL CRM TPK 225</t>
-  </si>
-  <si>
-    <t>20128754</t>
-  </si>
-  <si>
-    <t>FF SS.SEREAL CKL 225</t>
-  </si>
-  <si>
-    <t>20136769</t>
-  </si>
-  <si>
-    <t>F.FLAG UHT BERIS 225</t>
-  </si>
-  <si>
-    <t>20136768</t>
-  </si>
-  <si>
-    <t>F.FLAG UHT MATCH 225</t>
-  </si>
-  <si>
-    <t>20142233</t>
-  </si>
-  <si>
-    <t>INDOMILK JAPANE M180</t>
-  </si>
-  <si>
-    <t>10004669</t>
-  </si>
-  <si>
-    <t>ULTRA UHT CHOCO 250M</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>10004668</t>
-  </si>
-  <si>
-    <t>ULTRA UHT STRAW 250M</t>
-  </si>
-  <si>
-    <t>10004676</t>
-  </si>
-  <si>
-    <t>ULTRA PLAIN SLIM250M</t>
-  </si>
-  <si>
-    <t>10007380</t>
-  </si>
-  <si>
-    <t>ULTRA SLIM COKLAT200</t>
-  </si>
-  <si>
-    <t>10008095</t>
-  </si>
-  <si>
-    <t>ULTRA SLIM STRAW 200</t>
-  </si>
-  <si>
-    <t>10007379</t>
-  </si>
-  <si>
-    <t>ULTRA SLIM PLAIN 200</t>
-  </si>
-  <si>
-    <t>20090189</t>
-  </si>
-  <si>
-    <t>ULTRA SUSU KRML 200</t>
-  </si>
-  <si>
-    <t>20088964</t>
-  </si>
-  <si>
-    <t>ULTRA SUSU TARO 200</t>
-  </si>
-  <si>
-    <t>20138895</t>
-  </si>
-  <si>
-    <t>ULTRA UHT BLUBRY 200</t>
-  </si>
-  <si>
-    <t>20110968</t>
-  </si>
-  <si>
-    <t>MUJIGAE BNNA MLK 250</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>20110967</t>
-  </si>
-  <si>
-    <t>MUJIGAE CHOC BAN 250</t>
-  </si>
-  <si>
-    <t>20126897</t>
-  </si>
-  <si>
-    <t>MUJIGAE STRW BAN 250</t>
-  </si>
-  <si>
-    <t>20138050</t>
-  </si>
-  <si>
-    <t>MUJIGAE WTRMLN 250</t>
-  </si>
-  <si>
-    <t>20130518</t>
-  </si>
-  <si>
-    <t>TS ALMND.CHOCO 190ML</t>
-  </si>
-  <si>
-    <t>20118377</t>
-  </si>
-  <si>
-    <t>TS OAT VANILLA 190ML</t>
-  </si>
-  <si>
-    <t>20139295</t>
-  </si>
-  <si>
-    <t>BROOKFARM ORI 200ML</t>
-  </si>
-  <si>
-    <t>20139300</t>
-  </si>
-  <si>
-    <t>BROOKFARM MATCHA 200</t>
-  </si>
-  <si>
-    <t>20037974</t>
-  </si>
-  <si>
-    <t>ULTRA UHT MOKA 250</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>20139359</t>
-  </si>
-  <si>
-    <t>KIT KAT CHO KLG 220</t>
-  </si>
-  <si>
-    <t>10014404</t>
-  </si>
-  <si>
-    <t>MILO HEALTY DRINK220</t>
-  </si>
-  <si>
-    <t>20037607</t>
-  </si>
-  <si>
-    <t>MILO DRINK KLG 220ML</t>
-  </si>
-  <si>
-    <t>20135340</t>
-  </si>
-  <si>
-    <t>MILO DRNK EXT.CHO220</t>
-  </si>
-  <si>
-    <t>20136206</t>
-  </si>
-  <si>
-    <t>MILO DRNK COOL 220</t>
-  </si>
-  <si>
-    <t>20139358</t>
-  </si>
-  <si>
-    <t>MILO PRO UHT 225ML</t>
-  </si>
-  <si>
-    <t>20019597</t>
-  </si>
-  <si>
-    <t>MILO ACTIV-GO 180ML</t>
-  </si>
-  <si>
-    <t>20133873</t>
-  </si>
-  <si>
-    <t>MILO CHOCO BANANA180</t>
-  </si>
-  <si>
-    <t>20133871</t>
-  </si>
-  <si>
-    <t>MILO CHOCO CEREAL180</t>
-  </si>
-  <si>
-    <t>20047247</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL 750</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>20008767</t>
-  </si>
-  <si>
-    <t>CLUB AIR MNRAL 600ML</t>
-  </si>
-  <si>
-    <t>20090527</t>
-  </si>
-  <si>
-    <t>CRYSTALIN BTL 600mL</t>
-  </si>
-  <si>
-    <t>20077499</t>
-  </si>
-  <si>
-    <t>PRISTINE 8.6+ BTL600</t>
-  </si>
-  <si>
-    <t>20139699</t>
-  </si>
-  <si>
-    <t>OASIS  MNRL PH9 500</t>
-  </si>
-  <si>
-    <t>20061938</t>
-  </si>
-  <si>
-    <t>SUPER O2 SPRTVO 600</t>
-  </si>
-  <si>
-    <t>20056219</t>
-  </si>
-  <si>
-    <t>ETERNALPLUS BTL 500</t>
-  </si>
-  <si>
-    <t>20045052</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR MIN330</t>
-  </si>
-  <si>
-    <t>PT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>10015532</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL 330</t>
-  </si>
-  <si>
-    <t>20137991</t>
-  </si>
-  <si>
-    <t>AQUVIVA BTL 700ML</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>20037131</t>
-  </si>
-  <si>
-    <t>PRIM-A AIR MNRAL 600</t>
-  </si>
-  <si>
-    <t>20142495</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR MIN 1L</t>
-  </si>
-  <si>
-    <t>20069208</t>
-  </si>
-  <si>
-    <t>LE MINERALE 600ML</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>10003814</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL 600</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>10004336</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR MIN600</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>PT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20089542</t>
-  </si>
-  <si>
-    <t>IDM AIR MN 8+ BTL500</t>
-  </si>
-  <si>
-    <t>RT,(E-15H)</t>
-  </si>
-  <si>
-    <t>20052629</t>
-  </si>
-  <si>
-    <t>IDM AIR DGN OKSGN600</t>
-  </si>
-  <si>
-    <t>PT,(E-15H)</t>
-  </si>
-  <si>
-    <t>20005529</t>
-  </si>
-  <si>
-    <t>NESTLE PURE LIFE 600</t>
+    <t>998</t>
   </si>
 </sst>
 </file>
@@ -2710,13 +2719,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F355"/>
+  <dimension ref="A1:F356"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="5" width="4" customWidth="1"/>
+    <col min="4" max="4" width="5" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3774,7 +3784,7 @@
         <v>55</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>77</v>
@@ -3794,7 +3804,7 @@
         <v>55</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>77</v>
@@ -3811,13 +3821,13 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3834,7 +3844,7 @@
         <v>58</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>23</v>
@@ -3854,7 +3864,7 @@
         <v>58</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>23</v>
@@ -3874,7 +3884,7 @@
         <v>58</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>23</v>
@@ -3894,7 +3904,7 @@
         <v>58</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>23</v>
@@ -3914,7 +3924,7 @@
         <v>58</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>23</v>
@@ -3934,7 +3944,7 @@
         <v>58</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>23</v>
@@ -3954,7 +3964,7 @@
         <v>58</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>23</v>
@@ -3974,7 +3984,7 @@
         <v>58</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>23</v>
@@ -3994,7 +4004,7 @@
         <v>58</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>23</v>
@@ -4002,22 +4012,22 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="C65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F65" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -4031,13 +4041,13 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -4051,13 +4061,13 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -4071,10 +4081,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>31</v>
@@ -4091,10 +4101,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>31</v>
@@ -4111,10 +4121,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>31</v>
@@ -4131,13 +4141,13 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -4151,13 +4161,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -4171,10 +4181,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>23</v>
@@ -4191,33 +4201,33 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>164</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="E75" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -4231,13 +4241,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -4251,13 +4261,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>23</v>
+        <v>166</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -4271,10 +4281,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>23</v>
@@ -4291,13 +4301,13 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -4311,13 +4321,13 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -4331,30 +4341,30 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C82" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="E82" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>31</v>
@@ -4371,10 +4381,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>31</v>
@@ -4391,13 +4401,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -4411,13 +4421,13 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -4431,10 +4441,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>31</v>
@@ -4451,10 +4461,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>31</v>
@@ -4471,10 +4481,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>31</v>
@@ -4491,13 +4501,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -4511,10 +4521,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>23</v>
@@ -4531,30 +4541,30 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>144</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="E92" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>28</v>
@@ -4571,13 +4581,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -4591,13 +4601,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -4611,10 +4621,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>23</v>
@@ -4631,13 +4641,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -4651,13 +4661,13 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -4671,10 +4681,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>23</v>
@@ -4691,13 +4701,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -4711,10 +4721,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -4731,30 +4741,30 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>144</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>23</v>
@@ -4771,10 +4781,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>23</v>
@@ -4791,10 +4801,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>23</v>
@@ -4811,10 +4821,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>23</v>
@@ -4831,10 +4841,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>23</v>
@@ -4851,10 +4861,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>23</v>
@@ -4871,10 +4881,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>23</v>
@@ -4891,33 +4901,33 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>164</v>
+        <v>23</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="C110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -4931,13 +4941,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4951,13 +4961,13 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>23</v>
+        <v>166</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4971,10 +4981,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>23</v>
@@ -4991,10 +5001,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>23</v>
@@ -5011,10 +5021,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>23</v>
@@ -5031,10 +5041,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>23</v>
@@ -5051,10 +5061,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>23</v>
@@ -5071,10 +5081,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>23</v>
@@ -5082,19 +5092,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>23</v>
@@ -5111,10 +5121,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>23</v>
@@ -5131,10 +5141,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>23</v>
@@ -5151,10 +5161,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>23</v>
@@ -5171,10 +5181,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>23</v>
@@ -5191,10 +5201,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>23</v>
@@ -5211,10 +5221,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>23</v>
@@ -5231,50 +5241,50 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>274</v>
+        <v>23</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F127" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="E128" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>23</v>
@@ -5291,10 +5301,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>23</v>
@@ -5311,10 +5321,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>23</v>
@@ -5331,10 +5341,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>23</v>
@@ -5342,19 +5352,19 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="C132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="E132" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>23</v>
@@ -5371,10 +5381,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>23</v>
@@ -5391,10 +5401,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>23</v>
@@ -5411,10 +5421,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>23</v>
@@ -5431,10 +5441,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>23</v>
@@ -5451,10 +5461,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>23</v>
@@ -5471,10 +5481,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>23</v>
@@ -5482,19 +5492,19 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>23</v>
@@ -5511,10 +5521,10 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>23</v>
@@ -5531,10 +5541,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>23</v>
@@ -5551,10 +5561,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>23</v>
@@ -5571,10 +5581,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>23</v>
@@ -5591,13 +5601,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -5611,10 +5621,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>28</v>
@@ -5631,33 +5641,33 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="E147" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -5671,10 +5681,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -5691,13 +5701,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -5711,13 +5721,13 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -5731,13 +5741,13 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -5751,10 +5761,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>23</v>
@@ -5771,10 +5781,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>23</v>
@@ -5791,10 +5801,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>23</v>
@@ -5802,19 +5812,19 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="E155" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>23</v>
@@ -5831,10 +5841,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>23</v>
@@ -5851,10 +5861,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>23</v>
@@ -5871,10 +5881,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>23</v>
@@ -5891,10 +5901,10 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>23</v>
@@ -5911,13 +5921,13 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5931,10 +5941,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>31</v>
@@ -5951,10 +5961,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>31</v>
@@ -5971,30 +5981,30 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="C164" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="C164" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>354</v>
-      </c>
       <c r="E164" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>23</v>
@@ -6011,13 +6021,13 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -6031,13 +6041,13 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -6051,10 +6061,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>23</v>
@@ -6071,10 +6081,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>23</v>
@@ -6091,10 +6101,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>23</v>
@@ -6111,10 +6121,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>23</v>
@@ -6131,10 +6141,10 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>23</v>
@@ -6142,19 +6152,19 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="C172" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D172" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="C172" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>371</v>
-      </c>
       <c r="E172" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>23</v>
@@ -6171,10 +6181,10 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>23</v>
@@ -6191,10 +6201,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>23</v>
@@ -6211,10 +6221,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>23</v>
@@ -6231,10 +6241,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>23</v>
@@ -6251,10 +6261,10 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>23</v>
@@ -6271,33 +6281,33 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="E179" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -6311,10 +6321,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>23</v>
@@ -6331,33 +6341,33 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>393</v>
+        <v>23</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="C182" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F182" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F182" s="1" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -6371,13 +6381,13 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>23</v>
+        <v>395</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6391,13 +6401,13 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6411,10 +6421,10 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>28</v>
@@ -6431,33 +6441,33 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B187" s="1" t="s">
+      <c r="C187" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D187" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="C187" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="E187" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6471,13 +6481,13 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6491,13 +6501,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6511,13 +6521,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6531,13 +6541,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6551,10 +6561,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>31</v>
@@ -6571,13 +6581,13 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -6591,10 +6601,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>23</v>
@@ -6611,10 +6621,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>423</v>
+        <v>406</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>23</v>
@@ -6622,19 +6632,19 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="B196" s="1" t="s">
+      <c r="C196" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D196" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="C196" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="E196" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>23</v>
@@ -6651,10 +6661,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>23</v>
@@ -6671,10 +6681,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>23</v>
@@ -6691,10 +6701,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>23</v>
@@ -6711,10 +6721,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>23</v>
@@ -6731,10 +6741,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>23</v>
@@ -6751,10 +6761,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>23</v>
@@ -6771,10 +6781,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>23</v>
@@ -6791,10 +6801,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>442</v>
+        <v>425</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>23</v>
@@ -6802,19 +6812,19 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="B205" s="1" t="s">
+      <c r="C205" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="C205" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="E205" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>23</v>
@@ -6831,10 +6841,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>23</v>
@@ -6851,10 +6861,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>23</v>
@@ -6871,10 +6881,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>23</v>
@@ -6891,10 +6901,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>23</v>
@@ -6911,10 +6921,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>23</v>
@@ -6931,10 +6941,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>23</v>
@@ -6951,10 +6961,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>23</v>
@@ -7277,7 +7287,7 @@
         <v>38</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -7297,7 +7307,7 @@
         <v>55</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -7517,7 +7527,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -8314,7 +8324,7 @@
         <v>584</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>23</v>
@@ -8334,7 +8344,7 @@
         <v>584</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>23</v>
@@ -8534,7 +8544,7 @@
         <v>607</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F291" s="1" t="s">
         <v>23</v>
@@ -8914,7 +8924,7 @@
         <v>648</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>23</v>
@@ -9454,7 +9464,7 @@
         <v>705</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>23</v>
@@ -9697,7 +9707,7 @@
         <v>11</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -9817,6 +9827,26 @@
         <v>14</v>
       </c>
       <c r="F355" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A356" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B356" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D356" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="E356" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F356" s="1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/E/CLB07N.xlsx
+++ b/E/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="770">
   <si>
     <t/>
   </si>
@@ -304,7 +304,7 @@
     <t>20142024</t>
   </si>
   <si>
-    <t>COOLTOPIA MELON ORG</t>
+    <t>KK3 CLTPIA ML/ORG320</t>
   </si>
   <si>
     <t>20045996</t>
@@ -1778,12 +1778,6 @@
   </si>
   <si>
     <t>INDOMLK BANANA 180</t>
-  </si>
-  <si>
-    <t>20134956</t>
-  </si>
-  <si>
-    <t>INDOMILK GOGUMA 180</t>
   </si>
   <si>
     <t>20127735</t>
@@ -2719,7 +2713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F356"/>
+  <dimension ref="A1:F355"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -8204,7 +8198,7 @@
         <v>584</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>23</v>
@@ -8224,7 +8218,7 @@
         <v>584</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>23</v>
@@ -8244,7 +8238,7 @@
         <v>584</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>23</v>
@@ -8264,7 +8258,7 @@
         <v>584</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>23</v>
@@ -8284,7 +8278,7 @@
         <v>584</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>23</v>
@@ -8304,7 +8298,7 @@
         <v>584</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>23</v>
@@ -8324,7 +8318,7 @@
         <v>584</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>23</v>
@@ -8341,10 +8335,10 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>165</v>
+        <v>4</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>23</v>
@@ -8352,19 +8346,19 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="C282" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D282" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="B282" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="C282" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>607</v>
-      </c>
       <c r="E282" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>23</v>
@@ -8381,10 +8375,10 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>23</v>
@@ -8401,10 +8395,10 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>23</v>
@@ -8421,10 +8415,10 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>23</v>
@@ -8441,10 +8435,10 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>23</v>
@@ -8461,33 +8455,33 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>23</v>
+        <v>618</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>620</v>
+        <v>23</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -8501,10 +8495,10 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>23</v>
@@ -8521,10 +8515,10 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="F290" s="1" t="s">
         <v>23</v>
@@ -8541,33 +8535,33 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>144</v>
+        <v>4</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>23</v>
+        <v>618</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B292" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C292" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D292" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="B292" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="C292" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D292" s="1" t="s">
-        <v>629</v>
-      </c>
       <c r="E292" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8581,13 +8575,13 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8601,13 +8595,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8621,13 +8615,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8641,13 +8635,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8661,13 +8655,13 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8681,13 +8675,13 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8701,13 +8695,13 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8721,30 +8715,30 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>620</v>
+        <v>23</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B301" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="C301" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D301" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="B301" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="C301" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D301" s="1" t="s">
-        <v>648</v>
-      </c>
       <c r="E301" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>23</v>
@@ -8761,10 +8755,10 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>23</v>
@@ -8781,10 +8775,10 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>23</v>
@@ -8801,10 +8795,10 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>23</v>
@@ -8821,10 +8815,10 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>23</v>
@@ -8841,10 +8835,10 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>23</v>
@@ -8861,10 +8855,10 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>23</v>
@@ -8881,10 +8875,10 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>23</v>
@@ -8901,10 +8895,10 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>23</v>
@@ -8921,10 +8915,10 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>648</v>
+        <v>667</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>144</v>
+        <v>4</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>23</v>
@@ -8932,19 +8926,19 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B311" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="C311" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D311" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="B311" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="C311" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D311" s="1" t="s">
-        <v>669</v>
-      </c>
       <c r="E311" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>23</v>
@@ -8961,10 +8955,10 @@
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>23</v>
@@ -8981,10 +8975,10 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>23</v>
@@ -9001,10 +8995,10 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>23</v>
@@ -9021,10 +9015,10 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>23</v>
@@ -9041,10 +9035,10 @@
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>23</v>
@@ -9061,10 +9055,10 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>23</v>
@@ -9081,10 +9075,10 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>23</v>
@@ -9101,10 +9095,10 @@
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>669</v>
+        <v>686</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>23</v>
@@ -9112,19 +9106,19 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="B320" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="C320" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D320" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="B320" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="C320" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D320" s="1" t="s">
-        <v>688</v>
-      </c>
       <c r="E320" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>23</v>
@@ -9141,10 +9135,10 @@
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>23</v>
@@ -9161,10 +9155,10 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>23</v>
@@ -9181,10 +9175,10 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>23</v>
@@ -9201,10 +9195,10 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>23</v>
@@ -9221,10 +9215,10 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>23</v>
@@ -9241,10 +9235,10 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>23</v>
@@ -9261,10 +9255,10 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>688</v>
+        <v>703</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>23</v>
@@ -9272,19 +9266,19 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D328" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="B328" s="1" t="s">
-        <v>704</v>
-      </c>
-      <c r="C328" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>705</v>
-      </c>
       <c r="E328" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>23</v>
@@ -9301,13 +9295,13 @@
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -9321,10 +9315,10 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>31</v>
@@ -9341,13 +9335,13 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -9361,10 +9355,10 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>23</v>
@@ -9381,10 +9375,10 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>23</v>
@@ -9401,10 +9395,10 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>23</v>
@@ -9421,10 +9415,10 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>23</v>
@@ -9441,10 +9435,10 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="F336" s="1" t="s">
         <v>23</v>
@@ -9461,33 +9455,33 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>705</v>
+        <v>724</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>144</v>
+        <v>4</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="B338" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D338" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="B338" s="1" t="s">
-        <v>725</v>
-      </c>
-      <c r="C338" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D338" s="1" t="s">
-        <v>726</v>
-      </c>
       <c r="E338" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -9501,13 +9495,13 @@
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -9521,13 +9515,13 @@
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -9541,13 +9535,13 @@
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -9561,10 +9555,10 @@
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F342" s="1" t="s">
         <v>23</v>
@@ -9581,13 +9575,13 @@
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -9601,33 +9595,33 @@
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>31</v>
+        <v>739</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>741</v>
+        <v>28</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -9641,30 +9635,30 @@
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>726</v>
+        <v>744</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B347" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="C347" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D347" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="B347" s="1" t="s">
-        <v>745</v>
-      </c>
-      <c r="C347" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D347" s="1" t="s">
-        <v>746</v>
-      </c>
       <c r="E347" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F347" s="1" t="s">
         <v>23</v>
@@ -9681,13 +9675,13 @@
         <v>3</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>23</v>
+        <v>166</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -9701,113 +9695,113 @@
         <v>3</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>166</v>
+        <v>23</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>28</v>
+        <v>758</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D352" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="B352" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="C352" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D352" s="1" t="s">
-        <v>759</v>
-      </c>
       <c r="E352" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>766</v>
+        <v>23</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
@@ -9821,32 +9815,12 @@
         <v>3</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>759</v>
+        <v>769</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A356" s="1" t="s">
-        <v>769</v>
-      </c>
-      <c r="B356" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="C356" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D356" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="E356" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F356" s="1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/E/CLB07N.xlsx
+++ b/E/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2142" uniqueCount="774">
   <si>
     <t/>
   </si>
@@ -76,21 +76,36 @@
     <t>6</t>
   </si>
   <si>
+    <t>20124899</t>
+  </si>
+  <si>
+    <t>CHI/FRST LYC/FZY 480</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20124898</t>
+  </si>
+  <si>
+    <t>CHI/FRST WHT/PCH 480</t>
+  </si>
+  <si>
+    <t>20139698</t>
+  </si>
+  <si>
+    <t>AJE BIG NPS MADU 350</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
     <t>20129966</t>
   </si>
   <si>
     <t>N/P MINUMAN LIME 330</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139698</t>
-  </si>
-  <si>
-    <t>AJE BIG NPS MADU 350</t>
-  </si>
-  <si>
     <t>20127835</t>
   </si>
   <si>
@@ -100,21 +115,6 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20124899</t>
-  </si>
-  <si>
-    <t>CHI/FRST LYC/FZY 480</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20124898</t>
-  </si>
-  <si>
-    <t>CHI/FRST WHT/PCH 480</t>
-  </si>
-  <si>
     <t>20138893</t>
   </si>
   <si>
@@ -337,22 +337,34 @@
     <t>TEBS SPRK MIX FRT330</t>
   </si>
   <si>
+    <t>20120499</t>
+  </si>
+  <si>
+    <t>K/A SIGNT STRONG 200</t>
+  </si>
+  <si>
+    <t>20089792</t>
+  </si>
+  <si>
+    <t>K/A DRNK BLK COFF200</t>
+  </si>
+  <si>
+    <t>20143469</t>
+  </si>
+  <si>
+    <t>GJAH K/TBRK GL BT200</t>
+  </si>
+  <si>
     <t>20124713</t>
   </si>
   <si>
     <t>LUWAK KOPI+GULA 220</t>
   </si>
   <si>
-    <t>20120499</t>
-  </si>
-  <si>
-    <t>K/A SIGNT STRONG 200</t>
-  </si>
-  <si>
-    <t>20089792</t>
-  </si>
-  <si>
-    <t>K/A DRNK BLK COFF200</t>
+    <t>20078206</t>
+  </si>
+  <si>
+    <t>LUWAK WHT ORGL 220ML</t>
   </si>
   <si>
     <t>20123322</t>
@@ -379,12 +391,6 @@
     <t>ABC MILK COFFEE 180</t>
   </si>
   <si>
-    <t>20078206</t>
-  </si>
-  <si>
-    <t>LUWAK WHT ORGL 220ML</t>
-  </si>
-  <si>
     <t>20120904</t>
   </si>
   <si>
@@ -994,16 +1000,73 @@
     <t>TEBS TEA WT/SODA 500</t>
   </si>
   <si>
+    <t>20141981</t>
+  </si>
+  <si>
+    <t>DUM2 CHO MILK TEA330</t>
+  </si>
+  <si>
+    <t>20141980</t>
+  </si>
+  <si>
+    <t>DUM2 RYL MILK TEA330</t>
+  </si>
+  <si>
+    <t>20136363</t>
+  </si>
+  <si>
+    <t>ICHTN DARK CHOCO 300</t>
+  </si>
+  <si>
     <t>20093586</t>
   </si>
   <si>
     <t>ICHTN THAI M.COFF300</t>
   </si>
   <si>
-    <t>20136363</t>
-  </si>
-  <si>
-    <t>ICHTN DARK CHOCO 300</t>
+    <t>20040383</t>
+  </si>
+  <si>
+    <t>NU MILK TEA 330ML</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20069527</t>
+  </si>
+  <si>
+    <t>NU TEH TARIK 330ML</t>
+  </si>
+  <si>
+    <t>20128233</t>
+  </si>
+  <si>
+    <t>NU CHO TEA HZLTEA330</t>
+  </si>
+  <si>
+    <t>20138202</t>
+  </si>
+  <si>
+    <t>NU MATCHA LATTEA 330</t>
+  </si>
+  <si>
+    <t>20085054</t>
+  </si>
+  <si>
+    <t>ICHTN THAI M.TEA 300</t>
+  </si>
+  <si>
+    <t>20101102</t>
+  </si>
+  <si>
+    <t>ICHTN MLK GR.TEA 300</t>
+  </si>
+  <si>
+    <t>20113450</t>
+  </si>
+  <si>
+    <t>ICHITAN MLK BRWN 300</t>
   </si>
   <si>
     <t>20135599</t>
@@ -1018,63 +1081,6 @@
     <t>ICHITAN MLN MILK 300</t>
   </si>
   <si>
-    <t>20040383</t>
-  </si>
-  <si>
-    <t>NU MILK TEA 330ML</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20069527</t>
-  </si>
-  <si>
-    <t>NU TEH TARIK 330ML</t>
-  </si>
-  <si>
-    <t>20128233</t>
-  </si>
-  <si>
-    <t>NU CHO TEA HZLTEA330</t>
-  </si>
-  <si>
-    <t>20138202</t>
-  </si>
-  <si>
-    <t>NU MATCHA LATTEA 330</t>
-  </si>
-  <si>
-    <t>20141981</t>
-  </si>
-  <si>
-    <t>DUM2 CHO MILK TEA330</t>
-  </si>
-  <si>
-    <t>20141980</t>
-  </si>
-  <si>
-    <t>DUM2 RYL MILK TEA330</t>
-  </si>
-  <si>
-    <t>20085054</t>
-  </si>
-  <si>
-    <t>ICHTN THAI M.TEA 300</t>
-  </si>
-  <si>
-    <t>20101102</t>
-  </si>
-  <si>
-    <t>ICHTN MLK GR.TEA 300</t>
-  </si>
-  <si>
-    <t>20113450</t>
-  </si>
-  <si>
-    <t>ICHITAN MLK BRWN 300</t>
-  </si>
-  <si>
     <t>20113377</t>
   </si>
   <si>
@@ -1390,6 +1396,12 @@
     <t>PRRO ZROSGR BLBRY235</t>
   </si>
   <si>
+    <t>20019179</t>
+  </si>
+  <si>
+    <t>B/BRAND GOLD MALT140</t>
+  </si>
+  <si>
     <t>20069773</t>
   </si>
   <si>
@@ -1816,10 +1828,10 @@
     <t>DIAMOND UHT BBLGM200</t>
   </si>
   <si>
-    <t>20019179</t>
-  </si>
-  <si>
-    <t>B/BRAND GOLD MALT140</t>
+    <t>20090314</t>
+  </si>
+  <si>
+    <t>DIAMOND UHT F/C200ML</t>
   </si>
   <si>
     <t>20032643</t>
@@ -2713,7 +2725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F355"/>
+  <dimension ref="A1:F357"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2941,15 +2953,15 @@
         <v>14</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -2961,7 +2973,7 @@
         <v>17</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2981,7 +2993,7 @@
         <v>20</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -3001,7 +3013,7 @@
         <v>38</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -3221,7 +3233,7 @@
         <v>20</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -3241,7 +3253,7 @@
         <v>38</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -3261,7 +3273,7 @@
         <v>55</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -3281,7 +3293,7 @@
         <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -3301,7 +3313,7 @@
         <v>8</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -3321,7 +3333,7 @@
         <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -3341,7 +3353,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -3441,7 +3453,7 @@
         <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3461,7 +3473,7 @@
         <v>8</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -3481,7 +3493,7 @@
         <v>11</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -3501,7 +3513,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -3521,7 +3533,7 @@
         <v>17</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -3641,7 +3653,7 @@
         <v>11</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -3661,7 +3673,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -3681,7 +3693,7 @@
         <v>17</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -3701,7 +3713,7 @@
         <v>20</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -3721,7 +3733,7 @@
         <v>38</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -3735,13 +3747,13 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F51" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -3755,10 +3767,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>23</v>
@@ -3778,10 +3790,10 @@
         <v>55</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -3798,10 +3810,10 @@
         <v>55</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -3818,10 +3830,10 @@
         <v>55</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3835,13 +3847,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3858,10 +3870,10 @@
         <v>58</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -3878,10 +3890,10 @@
         <v>58</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -3898,10 +3910,10 @@
         <v>58</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -3918,10 +3930,10 @@
         <v>58</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -3938,10 +3950,10 @@
         <v>58</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -3958,10 +3970,10 @@
         <v>58</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3978,10 +3990,10 @@
         <v>58</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -3998,10 +4010,10 @@
         <v>58</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -4018,30 +4030,30 @@
         <v>58</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>144</v>
+        <v>58</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F66" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -4055,13 +4067,13 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -4075,13 +4087,13 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -4095,13 +4107,13 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -4115,13 +4127,13 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -4135,13 +4147,13 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -4155,13 +4167,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -4175,10 +4187,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>23</v>
@@ -4195,13 +4207,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -4215,33 +4227,33 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>166</v>
+        <v>28</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="E76" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -4255,13 +4267,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -4275,13 +4287,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>23</v>
+        <v>168</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -4295,13 +4307,13 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -4315,13 +4327,13 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -4335,10 +4347,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>23</v>
@@ -4355,33 +4367,33 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="C83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="E83" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -4395,13 +4407,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -4415,10 +4427,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>23</v>
@@ -4435,13 +4447,13 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -4455,13 +4467,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -4475,13 +4487,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -4495,13 +4507,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -4515,10 +4527,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>23</v>
@@ -4535,13 +4547,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>144</v>
+        <v>58</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -4555,10 +4567,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>146</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>28</v>
@@ -4566,22 +4578,22 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="C93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -4595,13 +4607,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -4615,13 +4627,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -4635,13 +4647,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -4655,10 +4667,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>28</v>
@@ -4675,13 +4687,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -4695,13 +4707,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -4715,13 +4727,13 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -4735,10 +4747,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>144</v>
+        <v>58</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -4755,33 +4767,33 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>146</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -4795,13 +4807,13 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -4815,13 +4827,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -4835,13 +4847,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -4855,13 +4867,13 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4875,13 +4887,13 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4895,13 +4907,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4915,33 +4927,33 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>166</v>
+        <v>28</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="C111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="E111" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4955,13 +4967,13 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4975,13 +4987,13 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>23</v>
+        <v>168</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -4995,13 +5007,13 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -5015,13 +5027,13 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -5035,13 +5047,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -5055,13 +5067,13 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -5075,13 +5087,13 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -5095,33 +5107,33 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="E120" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -5135,13 +5147,13 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -5155,13 +5167,13 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -5175,13 +5187,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -5195,13 +5207,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -5215,13 +5227,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -5235,13 +5247,13 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -5255,53 +5267,53 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>276</v>
+        <v>28</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F128" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="E129" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -5315,13 +5327,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -5335,13 +5347,13 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -5355,33 +5367,33 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="E133" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -5395,13 +5407,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -5415,13 +5427,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -5435,13 +5447,13 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -5455,13 +5467,13 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -5475,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -5495,33 +5507,33 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -5535,13 +5547,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -5555,13 +5567,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -5575,13 +5587,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -5595,13 +5607,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -5615,10 +5627,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>28</v>
@@ -5635,13 +5647,13 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -5655,33 +5667,33 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -5695,10 +5707,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -5715,13 +5727,13 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -5735,13 +5747,13 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -5755,13 +5767,13 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -5775,13 +5787,13 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -5795,13 +5807,13 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5815,10 +5827,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>23</v>
@@ -5826,22 +5838,22 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="E156" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5855,13 +5867,13 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -5875,13 +5887,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -5895,13 +5907,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5915,10 +5927,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>23</v>
@@ -5935,13 +5947,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5955,13 +5967,13 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -5975,13 +5987,13 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5995,33 +6007,33 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B165" s="1" t="s">
+      <c r="C165" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="C165" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>356</v>
-      </c>
       <c r="E165" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -6035,13 +6047,13 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -6055,13 +6067,13 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -6075,13 +6087,13 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -6095,13 +6107,13 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -6115,13 +6127,13 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -6135,13 +6147,13 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -6155,33 +6167,33 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>373</v>
-      </c>
       <c r="E173" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -6195,13 +6207,13 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -6215,13 +6227,13 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -6235,13 +6247,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -6255,13 +6267,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -6275,13 +6287,13 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -6295,10 +6307,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>28</v>
@@ -6306,22 +6318,22 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="C180" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="C180" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>388</v>
-      </c>
       <c r="E180" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -6335,13 +6347,13 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -6355,33 +6367,33 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>395</v>
+        <v>28</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F183" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F183" s="1" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6395,13 +6407,13 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>23</v>
+        <v>397</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6415,10 +6427,10 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>28</v>
@@ -6435,13 +6447,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -6455,33 +6467,33 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B188" s="1" t="s">
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="E188" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6495,13 +6507,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6515,13 +6527,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6535,13 +6547,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6555,13 +6567,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -6575,13 +6587,13 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -6595,10 +6607,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>23</v>
@@ -6615,13 +6627,13 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -6635,33 +6647,33 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B197" s="1" t="s">
+      <c r="C197" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D197" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="C197" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>425</v>
-      </c>
       <c r="E197" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -6675,13 +6687,13 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -6695,13 +6707,13 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -6715,13 +6727,13 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -6735,13 +6747,13 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -6755,13 +6767,13 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -6775,13 +6787,13 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -6795,13 +6807,13 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -6815,33 +6827,33 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>444</v>
+        <v>427</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B206" s="1" t="s">
+      <c r="C206" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="C206" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="E206" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -6855,13 +6867,13 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -6875,13 +6887,13 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -6895,13 +6907,13 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -6915,13 +6927,13 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6935,13 +6947,13 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6955,13 +6967,13 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -6975,53 +6987,53 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>463</v>
-      </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="B215" s="1" t="s">
+      <c r="C215" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D215" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="C215" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>461</v>
-      </c>
       <c r="E215" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -7035,13 +7047,13 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -7055,13 +7067,13 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -7075,13 +7087,13 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -7095,13 +7107,13 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -7115,10 +7127,10 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>28</v>
@@ -7135,13 +7147,13 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -7155,53 +7167,53 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="B223" s="1" t="s">
-        <v>482</v>
-      </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="B224" s="1" t="s">
+      <c r="C224" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D224" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="C224" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D224" s="1" t="s">
-        <v>480</v>
-      </c>
       <c r="E224" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -7215,13 +7227,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -7235,13 +7247,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -7255,13 +7267,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -7275,13 +7287,13 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>166</v>
+        <v>23</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -7295,13 +7307,13 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>166</v>
+        <v>23</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -7315,53 +7327,53 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>31</v>
+        <v>168</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="B231" s="1" t="s">
-        <v>499</v>
-      </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>31</v>
+        <v>168</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="B232" s="1" t="s">
+      <c r="C232" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D232" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="C232" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D232" s="1" t="s">
-        <v>497</v>
-      </c>
       <c r="E232" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -7375,13 +7387,13 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -7395,13 +7407,13 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -7415,10 +7427,10 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>23</v>
@@ -7435,10 +7447,10 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>23</v>
@@ -7455,53 +7467,53 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B238" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="B238" s="1" t="s">
-        <v>514</v>
-      </c>
       <c r="C238" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B239" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B239" s="1" t="s">
+      <c r="C239" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D239" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="C239" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D239" s="1" t="s">
-        <v>512</v>
-      </c>
       <c r="E239" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -7515,13 +7527,13 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>166</v>
+        <v>23</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -7535,53 +7547,53 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>521</v>
+        <v>23</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="B242" s="1" t="s">
-        <v>523</v>
-      </c>
       <c r="C242" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="B243" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="B243" s="1" t="s">
+      <c r="C243" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D243" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F243" s="1" t="s">
         <v>525</v>
-      </c>
-      <c r="C243" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D243" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="E243" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F243" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -7595,13 +7607,13 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -7615,13 +7627,13 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -7635,53 +7647,53 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="B247" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="B247" s="1" t="s">
-        <v>534</v>
-      </c>
       <c r="C247" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="B248" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="B248" s="1" t="s">
+      <c r="C248" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D248" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C248" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D248" s="1" t="s">
-        <v>532</v>
-      </c>
       <c r="E248" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -7695,13 +7707,13 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7715,10 +7727,10 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F250" s="1" t="s">
         <v>28</v>
@@ -7735,13 +7747,13 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -7755,13 +7767,13 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7775,13 +7787,13 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7795,10 +7807,10 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>23</v>
@@ -7806,19 +7818,19 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B255" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="B255" s="1" t="s">
-        <v>551</v>
-      </c>
       <c r="C255" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>23</v>
@@ -7826,22 +7838,22 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="B256" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="B256" s="1" t="s">
+      <c r="C256" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D256" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C256" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D256" s="1" t="s">
-        <v>549</v>
-      </c>
       <c r="E256" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -7855,13 +7867,13 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -7875,13 +7887,13 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7895,13 +7907,13 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7915,10 +7927,10 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>23</v>
@@ -7935,13 +7947,13 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7955,10 +7967,10 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>28</v>
@@ -7966,19 +7978,19 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B263" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="B263" s="1" t="s">
-        <v>565</v>
-      </c>
       <c r="C263" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>28</v>
@@ -7995,33 +8007,33 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D265" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="B265" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="C265" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D265" s="1" t="s">
-        <v>566</v>
-      </c>
       <c r="E265" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -8035,13 +8047,13 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -8055,13 +8067,13 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -8075,13 +8087,13 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -8095,13 +8107,13 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -8115,13 +8127,13 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -8135,53 +8147,53 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B272" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="B272" s="1" t="s">
-        <v>586</v>
-      </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B273" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="B273" s="1" t="s">
+      <c r="C273" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D273" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="C273" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D273" s="1" t="s">
-        <v>584</v>
-      </c>
       <c r="E273" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -8195,13 +8207,13 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -8215,13 +8227,13 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -8235,13 +8247,13 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -8255,13 +8267,13 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -8275,13 +8287,13 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -8295,13 +8307,13 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -8315,13 +8327,13 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -8335,53 +8347,53 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>4</v>
+        <v>146</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B282" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="B282" s="1" t="s">
-        <v>607</v>
-      </c>
       <c r="C282" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>8</v>
+        <v>167</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="B283" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="B283" s="1" t="s">
+      <c r="C283" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D283" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="C283" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D283" s="1" t="s">
-        <v>605</v>
-      </c>
       <c r="E283" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -8395,13 +8407,13 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -8415,13 +8427,13 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -8435,13 +8447,13 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -8455,53 +8467,53 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>618</v>
+        <v>28</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B288" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="B288" s="1" t="s">
-        <v>620</v>
-      </c>
       <c r="C288" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="B289" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="B289" s="1" t="s">
+      <c r="C289" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D289" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="E289" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F289" s="1" t="s">
         <v>622</v>
-      </c>
-      <c r="C289" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D289" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="E289" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F289" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -8515,13 +8527,13 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8535,53 +8547,53 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>618</v>
+        <v>28</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B292" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="B292" s="1" t="s">
-        <v>629</v>
-      </c>
       <c r="C292" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>8</v>
+        <v>146</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>618</v>
+        <v>28</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B293" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="B293" s="1" t="s">
+      <c r="C293" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D293" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="C293" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D293" s="1" t="s">
-        <v>627</v>
-      </c>
       <c r="E293" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8595,13 +8607,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8615,13 +8627,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8635,13 +8647,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8655,13 +8667,13 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8675,13 +8687,13 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8695,13 +8707,13 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8715,53 +8727,53 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>646</v>
+        <v>631</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>23</v>
+        <v>622</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B301" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="B301" s="1" t="s">
-        <v>648</v>
-      </c>
       <c r="C301" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>646</v>
+        <v>631</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>23</v>
+        <v>622</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="B302" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="B302" s="1" t="s">
+      <c r="C302" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D302" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="C302" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D302" s="1" t="s">
-        <v>646</v>
-      </c>
       <c r="E302" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -8775,13 +8787,13 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -8795,13 +8807,13 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -8815,13 +8827,13 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -8835,13 +8847,13 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -8855,13 +8867,13 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -8875,13 +8887,13 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -8895,13 +8907,13 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -8915,53 +8927,53 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>667</v>
+        <v>650</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B311" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="B311" s="1" t="s">
-        <v>669</v>
-      </c>
       <c r="C311" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>667</v>
+        <v>650</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>8</v>
+        <v>146</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="B312" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="B312" s="1" t="s">
+      <c r="C312" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D312" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="C312" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D312" s="1" t="s">
-        <v>667</v>
-      </c>
       <c r="E312" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -8975,13 +8987,13 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -8995,13 +9007,13 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -9015,13 +9027,13 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -9035,13 +9047,13 @@
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -9055,13 +9067,13 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -9075,13 +9087,13 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -9095,53 +9107,53 @@
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>686</v>
+        <v>671</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="B320" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="B320" s="1" t="s">
-        <v>688</v>
-      </c>
       <c r="C320" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>686</v>
+        <v>671</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="B321" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="B321" s="1" t="s">
+      <c r="C321" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D321" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="C321" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D321" s="1" t="s">
-        <v>686</v>
-      </c>
       <c r="E321" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -9155,13 +9167,13 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -9175,13 +9187,13 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -9195,13 +9207,13 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -9215,13 +9227,13 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -9235,13 +9247,13 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -9255,53 +9267,53 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>703</v>
+        <v>690</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B328" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="B328" s="1" t="s">
-        <v>705</v>
-      </c>
       <c r="C328" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>703</v>
+        <v>690</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B329" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="B329" s="1" t="s">
+      <c r="C329" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D329" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="C329" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D329" s="1" t="s">
-        <v>703</v>
-      </c>
       <c r="E329" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -9315,13 +9327,13 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -9335,10 +9347,10 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F331" s="1" t="s">
         <v>23</v>
@@ -9355,10 +9367,10 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>23</v>
@@ -9375,13 +9387,13 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -9395,13 +9407,13 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -9415,13 +9427,13 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -9435,13 +9447,13 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -9455,10 +9467,10 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>724</v>
+        <v>707</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>28</v>
@@ -9466,42 +9478,42 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="B338" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="B338" s="1" t="s">
-        <v>726</v>
-      </c>
       <c r="C338" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>724</v>
+        <v>707</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>8</v>
+        <v>146</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="B339" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="B339" s="1" t="s">
+      <c r="C339" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D339" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="C339" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D339" s="1" t="s">
-        <v>724</v>
-      </c>
       <c r="E339" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -9515,13 +9527,13 @@
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -9535,13 +9547,13 @@
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -9555,10 +9567,10 @@
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F342" s="1" t="s">
         <v>23</v>
@@ -9575,13 +9587,13 @@
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -9595,93 +9607,93 @@
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>739</v>
+        <v>28</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B345" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="B345" s="1" t="s">
-        <v>741</v>
-      </c>
       <c r="C345" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="B346" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="B346" s="1" t="s">
+      <c r="C346" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D346" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="E346" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F346" s="1" t="s">
         <v>743</v>
-      </c>
-      <c r="C346" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D346" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="E346" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F346" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="B347" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="B347" s="1" t="s">
-        <v>746</v>
-      </c>
       <c r="C347" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>744</v>
+        <v>728</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="B348" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="B348" s="1" t="s">
+      <c r="C348" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D348" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="C348" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D348" s="1" t="s">
-        <v>744</v>
-      </c>
       <c r="E348" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>166</v>
+        <v>28</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -9695,133 +9707,173 @@
         <v>3</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B350" s="1" t="s">
         <v>752</v>
       </c>
-      <c r="B350" s="1" t="s">
-        <v>753</v>
-      </c>
       <c r="C350" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="B351" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="C351" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D351" s="1" t="s">
         <v>755</v>
-      </c>
-      <c r="B351" s="1" t="s">
-        <v>756</v>
-      </c>
-      <c r="C351" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D351" s="1" t="s">
-        <v>757</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>758</v>
+        <v>28</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>761</v>
+        <v>33</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="C353" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D353" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="E353" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F353" s="1" t="s">
         <v>762</v>
-      </c>
-      <c r="B353" s="1" t="s">
-        <v>763</v>
-      </c>
-      <c r="C353" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D353" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="E353" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F353" s="1" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="B354" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="E354" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F354" s="1" t="s">
         <v>765</v>
-      </c>
-      <c r="B354" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="C354" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D354" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="E354" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F354" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="B355" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="B355" s="1" t="s">
+      <c r="C355" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="E355" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F355" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="C355" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D355" s="1" t="s">
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A356" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="E355" s="1" t="s">
+      <c r="B356" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D356" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="E356" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F356" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A357" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="B357" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="C357" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D357" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="E357" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F355" s="1" t="s">
-        <v>23</v>
+      <c r="F357" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
